--- a/data/source/Stainless_Steel_Carbon_Accounting_Grid_5.xlsx
+++ b/data/source/Stainless_Steel_Carbon_Accounting_Grid_5.xlsx
@@ -2056,7 +2056,7 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>x*0.14+y*0.07</t>
+          <t>x*0.14+y*0.1</t>
         </is>
       </c>
       <c r="P14" s="5" t="inlineStr">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>x*0.126667+y*0.056</t>
+          <t>x*0.126667+y*0.08</t>
         </is>
       </c>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>(x*0.000233333+y*0.000056)*28</t>
+          <t>(x*0.000233333+y*0.00008)*28</t>
         </is>
       </c>
       <c r="T14" s="5" t="inlineStr">
         <is>
-          <t>(x*0.00000833333+y*0.0000056)*265</t>
+          <t>(x*0.00000833333+y*0.000008)*265</t>
         </is>
       </c>
       <c r="U14" s="5" t="inlineStr">
@@ -2112,13 +2112,13 @@
       <c r="Z14" s="6" t="inlineStr">
         <is>
           <t>Coefficients used in this row's formulas (Grid 5 calibration, Melt Shop — replace with verified plant/EPD data before regulatory use):
-EF_S1_virgin=0.14, EF_S1_scrap=0.07 tCO2e/t | EF_S2_virgin=0.5005, EF_S2_scrap=0.3542 tCO2e/t | EF_S3_virgin=3.2, EF_S3_scrap=0.2 tCO2e/t
-CO2_v=0.126667, CO2_s=0.056 t/t | CH4_v=0.000233333, CH4_s=0.000056 t/t (x28) | N2O_v=0.00000833333, N2O_s=0.0000056 t/t (x265)
+EF_S1_virgin=0.14, EF_S1_scrap=0.1 tCO2e/t | EF_S2_virgin=0.5005, EF_S2_scrap=0.3542 tCO2e/t | EF_S3_virgin=3.2, EF_S3_scrap=0.2 tCO2e/t
+CO2_v=0.126667, CO2_s=0.08 t/t | CH4_v=0.000233333, CH4_s=0.00008 t/t (x28) | N2O_v=0.00000833333, N2O_s=0.000008 t/t (x265)
 HFC_v=0.0001144, HFC_s=0.000168667 tCO2e/t | PFC_v=0.0000286, PFC_s=0.0000421667 tCO2e/t | SF6_v=0.0000001144, SF6_s=0.000000168667 t/t (x23500) | NF3_v=0.00000001144, NF3_s=0.000000016867 t/t (x16100)
 SEC_virgin=3.1 GJ/t, SEC_scrap=2.1 GJ/t.
 Basis: Standard scrap-EAF; virgin-side reflects ferrochrome/ferronickel/DRI charge requiring more melt energy and reduction-related Scope 1 than pure scrap remelt. CEA grid basis for Scope 2. Illustrative literature-typical values — NOT plant-measured.
 Scope 2 CUSTOMIZED: underlying electricity intensity backed out at the CEA-baseline reference (0.77 kg CO2e/kWh) = 650 kWh/t (virgin), 460 kWh/t (scrap). Actual Scope 2 now scales with your real grid mix (a-g) — see 'Grid Energy Mix Factors' sheet for per-source factors.
-Grid 5 calibration: Stainless EAF melts scrap at ~420-480 kWh/t; a virgin-heavy charge (ferroalloys, pig iron, DRI) needs more, ~600-700 kWh/t. Direct emissions from electrodes (~2 kg/t), charge carbon and burners are ~0.06-0.15 tCO2/t. Grid 4 → Grid 5 (virgin/scrap): kWh/t 2272.73/545.455 → 650/460; Scope 1 0.42/0.05 → 0.14/0.07; Scope 3 1.1/0.12 → 3.2/0.2; SEC GJ/t 23/5.8 → 3.1/2.1.</t>
+Grid 5 calibration: Stainless EAF melts scrap at ~420-480 kWh/t; a virgin-heavy charge (ferroalloys, pig iron, DRI) needs more, ~600-700 kWh/t. Direct emissions from electrodes (1.2-3 kg/t), charge carbon and burners: ~0.10 tCO2/t on scrap (typical EAF ~102 kg/t), more on a carbon-rich virgin charge. Grid 4 → Grid 5 (virgin/scrap): kWh/t 2272.73/545.455 → 650/460; Scope 1 0.42/0.05 → 0.14/0.1; Scope 3 1.1/0.12 → 3.2/0.2; SEC GJ/t 23/5.8 → 3.1/2.1.</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>x*0.06+y*0.04</t>
+          <t>x*0.09+y*0.05</t>
         </is>
       </c>
       <c r="P20" s="5" t="inlineStr">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="R20" s="5" t="inlineStr">
         <is>
-          <t>x*0.09+y*0.03</t>
+          <t>x*0.135+y*0.0375</t>
         </is>
       </c>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>(x*0.00002+y*0.00001)*28</t>
+          <t>(x*0.00003+y*0.0000125)*28</t>
         </is>
       </c>
       <c r="T20" s="5" t="inlineStr">
         <is>
-          <t>(x*0.000001+y*0.0000005)*265</t>
+          <t>(x*0.0000015+y*0.000000625)*265</t>
         </is>
       </c>
       <c r="U20" s="5" t="inlineStr">
@@ -2946,13 +2946,13 @@
       <c r="Z20" s="6" t="inlineStr">
         <is>
           <t>Coefficients used in this row's formulas (Grid 5 calibration, Melt Shop — replace with verified plant/EPD data before regulatory use):
-EF_S1_virgin=0.06, EF_S1_scrap=0.04 tCO2e/t | EF_S2_virgin=0.0462, EF_S2_scrap=0.03465 tCO2e/t | EF_S3_virgin=0.2, EF_S3_scrap=0.08 tCO2e/t
-CO2_v=0.09, CO2_s=0.03 t/t | CH4_v=0.00002, CH4_s=0.00001 t/t (x28) | N2O_v=0.000001, N2O_s=0.0000005 t/t (x265)
+EF_S1_virgin=0.09, EF_S1_scrap=0.05 tCO2e/t | EF_S2_virgin=0.0462, EF_S2_scrap=0.03465 tCO2e/t | EF_S3_virgin=0.2, EF_S3_scrap=0.08 tCO2e/t
+CO2_v=0.135, CO2_s=0.0375 t/t | CH4_v=0.00003, CH4_s=0.0000125 t/t (x28) | N2O_v=0.0000015, N2O_s=0.000000625 t/t (x265)
 HFC_v=0.0000308, HFC_s=0.000017325 tCO2e/t | PFC_v=0.00000616, PFC_s=0.000003465 tCO2e/t | SF6_v=0.0000000616, SF6_s=0.00000003465 t/t (x23500) | NF3_v=0.00000000616, NF3_s=0.000000003465 t/t (x16100)
 SEC_virgin=0.9 GJ/t, SEC_scrap=0.6 GJ/t.
 Basis: Argon-Oxygen Decarburization — most common global stainless decarb route; CO2 is dominated by actual process decarburization (carbon oxidized out of the melt), not fuel combustion. Illustrative literature-typical values — NOT plant-measured.
 Scope 2 CUSTOMIZED: underlying electricity intensity backed out at the CEA-baseline reference (0.77 kg CO2e/kWh) = 60 kWh/t (virgin), 45 kWh/t (scrap). Actual Scope 2 now scales with your real grid mix (a-g) — see 'Grid Energy Mix Factors' sheet for per-source factors.
-Grid 5 calibration: AOD needs little electricity of its own; oxygen, argon and nitrogen supply plus fume extraction come to ~40-60 kWh/t. Decarburisation CO2 left as in Grid 4. Grid 4 → Grid 5 (virgin/scrap): kWh/t 194.805/129.87 → 60/45; SEC GJ/t 3.5/2 → 0.9/0.6.</t>
+Grid 5 calibration: AOD needs little electricity of its own; oxygen, argon and nitrogen supply plus fume extraction come to ~40-60 kWh/t. Decarburising from ~1.5-2.5% C (more on a high-carbon ferrochrome charge) to &lt;0.05% C releases ~0.05-0.09 tCO2/t. Grid 4 → Grid 5 (virgin/scrap): kWh/t 194.805/129.87 → 60/45; Scope 1 0.06/0.04 → 0.09/0.05; SEC GJ/t 3.5/2 → 0.9/0.6.</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>x*0.06+y*0.04</t>
+          <t>x*0.09+y*0.05</t>
         </is>
       </c>
       <c r="P23" s="5" t="inlineStr">
@@ -3322,17 +3322,17 @@
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
-          <t>x*0.088+y*0.03</t>
+          <t>x*0.132+y*0.0375</t>
         </is>
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>(x*0.00002+y*0.00001)*28</t>
+          <t>(x*0.00003+y*0.0000125)*28</t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr">
         <is>
-          <t>(x*0.000001+y*0.0000005)*265</t>
+          <t>(x*0.0000015+y*0.000000625)*265</t>
         </is>
       </c>
       <c r="U23" s="5" t="inlineStr">
@@ -3363,13 +3363,13 @@
       <c r="Z23" s="6" t="inlineStr">
         <is>
           <t>Coefficients used in this row's formulas (Grid 5 calibration, Melt Shop — replace with verified plant/EPD data before regulatory use):
-EF_S1_virgin=0.06, EF_S1_scrap=0.04 tCO2e/t | EF_S2_virgin=0.05005, EF_S2_scrap=0.03696 tCO2e/t | EF_S3_virgin=0.21, EF_S3_scrap=0.085 tCO2e/t
-CO2_v=0.088, CO2_s=0.03 t/t | CH4_v=0.00002, CH4_s=0.00001 t/t (x28) | N2O_v=0.000001, N2O_s=0.0000005 t/t (x265)
+EF_S1_virgin=0.09, EF_S1_scrap=0.05 tCO2e/t | EF_S2_virgin=0.05005, EF_S2_scrap=0.03696 tCO2e/t | EF_S3_virgin=0.21, EF_S3_scrap=0.085 tCO2e/t
+CO2_v=0.132, CO2_s=0.0375 t/t | CH4_v=0.00003, CH4_s=0.0000125 t/t (x28) | N2O_v=0.0000015, N2O_s=0.000000625 t/t (x265)
 HFC_v=0.0000312812, HFC_s=0.00001848 tCO2e/t | PFC_v=0.00000625625, PFC_s=0.000003696 tCO2e/t | SF6_v=0.000000062563, SF6_s=0.00000003696 t/t (x23500) | NF3_v=0.000000006256, NF3_s=0.000000003696 t/t (x16100)
 SEC_virgin=1 GJ/t, SEC_scrap=0.7 GJ/t.
 Basis: Creusot-Loire Uddeholm process — steam/O2/Ar/N2 blowing, similar purpose to AOD; steam generation adds a modest SEC premium over AOD. Illustrative literature-typical values — NOT plant-measured.
 Scope 2 CUSTOMIZED: underlying electricity intensity backed out at the CEA-baseline reference (0.77 kg CO2e/kWh) = 65 kWh/t (virgin), 48 kWh/t (scrap). Actual Scope 2 now scales with your real grid mix (a-g) — see 'Grid Energy Mix Factors' sheet for per-source factors.
-Grid 5 calibration: CLU: as AOD with steam dilution, ~50-65 kWh/t. Grid 4 → Grid 5 (virgin/scrap): kWh/t 207.792/129.87 → 65/48; SEC GJ/t 3.6/2.1 → 1/0.7.</t>
+Grid 5 calibration: CLU: as AOD with steam dilution, ~50-65 kWh/t; same decarburisation CO2. Grid 4 → Grid 5 (virgin/scrap): kWh/t 207.792/129.87 → 65/48; Scope 1 0.06/0.04 → 0.09/0.05; SEC GJ/t 3.6/2.1 → 1/0.7.</t>
         </is>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10645,1260 +10645,760 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>EAF electricity, scrap / cold DRI charge</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>385 / 590 kWh/t</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>Thermodynamic and plant studies of EAF electrical demand.</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>EAF graphite electrode consumption</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>1.2-3.0 kg/t</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>Varies with grade and practice; ~1.4 kg/t average across many EAFs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>EAF direct CO2, typical</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>~102 kg CO2/t</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Electrodes, charge and foaming carbon, decarburisation, burners.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Ladle furnace electricity</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>~27.5 kWh/t average; 65 kWh/t with gas cleaning</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Plant average and best-practice figure incl. fume system.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Cold rolling, best practice (carbon sheet)</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>87 kWh/t</t>
+        </is>
+      </c>
+      <c r="C17" s="16" t="inlineStr">
+        <is>
+          <t>LBNL world best practice; stainless on cluster mills runs higher (150-300 kWh/t cited).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Walking-beam reheating fuel</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>~1.1-1.5 GJ/t</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>Conventional slab reheating; ~0.06-0.085 tCO2/t on natural gas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>High-carbon ferrochrome footprint</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>1.8-5.5 tCO2e/t FeCr (4.7-6.1 on coal power)</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>JOM 2023 (Energy Consumption and GHG Emissions of HC FeCr Production).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Nickel pig iron footprint</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>~7 tCO2e/t alloy (60-85 t per t Ni)</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>Energies 2020 (Nickel products); CarbonChain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Stainless EAF corporate footprint</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="inlineStr">
+        <is>
+          <t>4.57 tCO2e/t, ~70% Scope 3</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>ACS Sust. Resour. Manage. (Scope 3 in stainless EAF steelmaking); ferroalloys ~80% of Scope 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>Grid source factors</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>coal ~0.95; gas ~0.45; hydro 0.024, wind 0.011, solar PV ~0.045, nuclear 0.012</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Combustion factors for fossil; IPCC AR5 lifecycle medians for non-fossil. Kept from Grid 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Department</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>Technique / Process</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>Variation</t>
         </is>
       </c>
-      <c r="E14" s="18" t="inlineStr">
+      <c r="E24" s="18" t="inlineStr">
         <is>
           <t>Grid 4 kWh/t (v)</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F24" s="18" t="inlineStr">
         <is>
           <t>Grid 5 kWh/t (v)</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Grid 4 kWh/t (s)</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Grid 5 kWh/t (s)</t>
         </is>
       </c>
-      <c r="I14" s="18" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>Grid 4 Scope 1 (v/s)</t>
         </is>
       </c>
-      <c r="J14" s="18" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>Grid 5 Scope 1 (v/s)</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr">
         <is>
           <t>Grid 4 Scope 3 (v/s)</t>
         </is>
       </c>
-      <c r="L14" s="18" t="inlineStr">
+      <c r="L24" s="18" t="inlineStr">
         <is>
           <t>Grid 5 Scope 3 (v/s)</t>
         </is>
       </c>
-      <c r="M14" s="18" t="inlineStr">
+      <c r="M24" s="18" t="inlineStr">
         <is>
           <t>Grid 4 SEC (v/s)</t>
         </is>
       </c>
-      <c r="N14" s="18" t="inlineStr">
+      <c r="N24" s="18" t="inlineStr">
         <is>
           <t>Grid 5 SEC (v/s)</t>
         </is>
       </c>
-      <c r="O14" s="18" t="inlineStr">
+      <c r="O24" s="18" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>Unloading / Inbound</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>Train + Road Mix (p/q)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr"/>
-      <c r="M15" s="16" t="inlineStr"/>
-      <c r="N15" s="16" t="inlineStr"/>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Transport row: unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>Ferroalloy</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="H16" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.001</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.001</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0005</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0005</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.015</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.015</t>
-        </is>
-      </c>
-      <c r="O16" s="16" t="inlineStr">
-        <is>
-          <t>Inspection is already near-negligible; unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>Inspection</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>Scrap</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>1.16883</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>1.55844</v>
-      </c>
-      <c r="H17" s="16" t="n">
-        <v>1.55844</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.0015</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.0015</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0006</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0006</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.02</t>
-        </is>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.02</t>
-        </is>
-      </c>
-      <c r="O17" s="16" t="inlineStr">
-        <is>
-          <t>Inspection is already near-negligible; unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>Scrap Sorting / Processing / Preparation</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="n">
-        <v>1.2987</v>
-      </c>
-      <c r="F18" s="16" t="n">
-        <v>0.7792210000000001</v>
-      </c>
-      <c r="G18" s="16" t="n">
-        <v>36.3636</v>
-      </c>
-      <c r="H18" s="16" t="n">
-        <v>21.8182</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>0.002 / 0.035</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>0.0007 / 0.01225</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.002</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.002</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>0.02 / 0.65</t>
-        </is>
-      </c>
-      <c r="N18" s="16" t="inlineStr">
-        <is>
-          <t>0.0122647 / 0.244086</t>
-        </is>
-      </c>
-      <c r="O18" s="16" t="inlineStr">
-        <is>
-          <t>Scrap shredding and baling draws ~20-25 kWh per tonne of scrap; yard diesel for mobile handling ~3-5 L/t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>Sizing / Cutting / Screening</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="n">
-        <v>12.987</v>
-      </c>
-      <c r="F19" s="16" t="n">
-        <v>4.54545</v>
-      </c>
-      <c r="G19" s="16" t="n">
-        <v>19.4805</v>
-      </c>
-      <c r="H19" s="16" t="n">
-        <v>6.81818</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>0.008 / 0.02</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>0.0032 / 0.008</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0008</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0008</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>0.28 / 0.4</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>0.0596069 / 0.132654</t>
-        </is>
-      </c>
-      <c r="O19" s="16" t="inlineStr">
-        <is>
-          <t>Sizing and screening: ~4-8 kWh/t and light mobile-plant diesel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>Bedding / Stacking / Stockyard</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="n">
-        <v>15.5844</v>
-      </c>
-      <c r="F20" s="16" t="n">
-        <v>4.67532</v>
-      </c>
-      <c r="G20" s="16" t="n">
-        <v>6.49351</v>
-      </c>
-      <c r="H20" s="16" t="n">
-        <v>1.94805</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>0.01 / 0.008</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>0.004 / 0.0032</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>0.0003 / 0.0003</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>0.0003 / 0.0003</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>0.22 / 0.15</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>0.0708852 / 0.0502562</t>
-        </is>
-      </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>Stockyard stacking and reclaiming: ~3-5 kWh/t; mobile plant diesel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>Proportioning / Charge Basket</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n">
-        <v>7.79221</v>
-      </c>
-      <c r="F21" s="16" t="n">
-        <v>2.33766</v>
-      </c>
-      <c r="G21" s="16" t="n">
-        <v>15.5844</v>
-      </c>
-      <c r="H21" s="16" t="n">
-        <v>4.67532</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.002</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.002</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>0.0002 / 0.0002</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>0.0002 / 0.0002</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>0.1 / 0.18</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>0.0219291 / 0.0438582</t>
-        </is>
-      </c>
-      <c r="O21" s="16" t="inlineStr">
-        <is>
-          <t>Charge-bucket make-up: cranes and weighing, ~2-4 kWh/t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>RMHS</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>Internal Conveying / Furnace Feeding</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n">
-        <v>19.4805</v>
-      </c>
-      <c r="F22" s="16" t="n">
-        <v>4.87013</v>
-      </c>
-      <c r="G22" s="16" t="n">
-        <v>23.3766</v>
-      </c>
-      <c r="H22" s="16" t="n">
-        <v>5.84416</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0008</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>0.0005 / 0.0008</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>0.0001 / 0.0001</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>0.0001 / 0.0001</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>0.12 / 0.15</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>0.0242892 / 0.0318498</t>
-        </is>
-      </c>
-      <c r="O22" s="16" t="inlineStr">
-        <is>
-          <t>Belt conveying is ~0.5-1 kWh per tonne per km; in-plant runs total ~3-6 kWh/t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>Melt Shop</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>Scrap Prep / Charging</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>12.987</v>
-      </c>
-      <c r="F23" s="16" t="n">
-        <v>4.54545</v>
-      </c>
-      <c r="G23" s="16" t="n">
-        <v>32.4675</v>
-      </c>
-      <c r="H23" s="16" t="n">
-        <v>11.3636</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>0.005 / 0.01</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>0.005 / 0.01</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.001</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>0.001 / 0.001</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>0.15 / 0.25</t>
-        </is>
-      </c>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>0.105649 / 0.219481</t>
-        </is>
-      </c>
-      <c r="O23" s="16" t="inlineStr">
-        <is>
-          <t>Scrap charging cranes and magnets: ~4-10 kWh/t.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>Melt Shop</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>Primary Melting</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>Electric Arc Furnace (EAF)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="n">
-        <v>2272.73</v>
-      </c>
-      <c r="F24" s="16" t="n">
-        <v>650</v>
-      </c>
-      <c r="G24" s="16" t="n">
-        <v>545.455</v>
-      </c>
-      <c r="H24" s="16" t="n">
-        <v>460</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>0.42 / 0.05</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>0.14 / 0.07</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>1.1 / 0.12</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>3.2 / 0.2</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>23 / 5.8</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>3.1 / 2.1</t>
-        </is>
-      </c>
-      <c r="O24" s="16" t="inlineStr">
-        <is>
-          <t>Stainless EAF melts scrap at ~420-480 kWh/t; a virgin-heavy charge (ferroalloys, pig iron, DRI) needs more, ~600-700 kWh/t. Direct emissions from electrodes (~2 kg/t), charge carbon and burners are ~0.06-0.15 tCO2/t.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>Primary Melting</t>
+          <t>Unloading / Inbound</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>Induction Furnace (IF)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>1428.57</v>
-      </c>
-      <c r="F25" s="16" t="n">
-        <v>750</v>
-      </c>
-      <c r="G25" s="16" t="n">
-        <v>454.545</v>
-      </c>
-      <c r="H25" s="16" t="n">
-        <v>600</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>0.02 / 0.01</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>0.02 / 0.01</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>0.9 / 0.1</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>3.2 / 0.2</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>18 / 4.5</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>2.8 / 2.2</t>
-        </is>
-      </c>
+          <t>Train + Road Mix (p/q)</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr"/>
+      <c r="F25" s="16" t="inlineStr"/>
+      <c r="G25" s="16" t="inlineStr"/>
+      <c r="H25" s="16" t="inlineStr"/>
+      <c r="I25" s="16" t="inlineStr"/>
+      <c r="J25" s="16" t="inlineStr"/>
+      <c r="K25" s="16" t="inlineStr"/>
+      <c r="L25" s="16" t="inlineStr"/>
+      <c r="M25" s="16" t="inlineStr"/>
+      <c r="N25" s="16" t="inlineStr"/>
       <c r="O25" s="16" t="inlineStr">
         <is>
-          <t>Induction furnaces melt scrap at ~550-650 kWh/t with negligible direct emissions.</t>
+          <t>Transport row: unchanged.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
         <is>
-          <t>Primary Melting</t>
+          <t>Inspection</t>
         </is>
       </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
-          <t>Integrated BF/Converter</t>
+          <t>Ferroalloy</t>
         </is>
       </c>
       <c r="E26" s="16" t="n">
-        <v>454.545</v>
+        <v>1.16883</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>300</v>
+        <v>1.16883</v>
       </c>
       <c r="G26" s="16" t="n">
-        <v>64.93510000000001</v>
+        <v>1.16883</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>65</v>
+        <v>1.16883</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
-          <t>1.8 / 0.05</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>1.8 / 0.05</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="K26" s="16" t="inlineStr">
         <is>
-          <t>1.5 / 0.15</t>
+          <t>0.0005 / 0.0005</t>
         </is>
       </c>
       <c r="L26" s="16" t="inlineStr">
         <is>
-          <t>1.8 / 0.2</t>
+          <t>0.0005 / 0.0005</t>
         </is>
       </c>
       <c r="M26" s="16" t="inlineStr">
         <is>
-          <t>32 / 5</t>
+          <t>0.015 / 0.015</t>
         </is>
       </c>
       <c r="N26" s="16" t="inlineStr">
         <is>
-          <t>19 / 3.5</t>
+          <t>0.015 / 0.015</t>
         </is>
       </c>
       <c r="O26" s="16" t="inlineStr">
         <is>
-          <t>Integrated BF/converter: Scope 1 already carries the iron-making reductant (~1.8 tCO2/t hot metal), so Scope 3 carries only the alloy units; electricity for blast, oxygen and auxiliaries ~250-350 kWh/t.</t>
+          <t>Inspection is already near-negligible; unchanged.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
         <is>
-          <t>Primary Melting</t>
+          <t>Inspection</t>
         </is>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Vacuum / Special Induction (VIM)</t>
+          <t>Scrap</t>
         </is>
       </c>
       <c r="E27" s="16" t="n">
-        <v>2857.14</v>
+        <v>1.16883</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>1000</v>
+        <v>1.16883</v>
       </c>
       <c r="G27" s="16" t="n">
-        <v>714.2859999999999</v>
+        <v>1.55844</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>800</v>
+        <v>1.55844</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.015</t>
+          <t>0.001 / 0.0015</t>
         </is>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.015</t>
+          <t>0.001 / 0.0015</t>
         </is>
       </c>
       <c r="K27" s="16" t="inlineStr">
         <is>
-          <t>1.3 / 0.12</t>
+          <t>0.0005 / 0.0006</t>
         </is>
       </c>
       <c r="L27" s="16" t="inlineStr">
         <is>
-          <t>3.2 / 0.2</t>
+          <t>0.0005 / 0.0006</t>
         </is>
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>45 / 15</t>
+          <t>0.015 / 0.02</t>
         </is>
       </c>
       <c r="N27" s="16" t="inlineStr">
         <is>
-          <t>3.8 / 3.1</t>
+          <t>0.015 / 0.02</t>
         </is>
       </c>
       <c r="O27" s="16" t="inlineStr">
         <is>
-          <t>Vacuum induction melting runs ~800-1,000 kWh/t.</t>
+          <t>Inspection is already near-negligible; unchanged.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
         <is>
-          <t>Primary Melting</t>
+          <t>Scrap Sorting / Processing / Preparation</t>
         </is>
       </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
-          <t>Vacuum Arc Remelting (VAR)</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E28" s="16" t="n">
-        <v>3636.36</v>
+        <v>1.2987</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>1300</v>
+        <v>0.7792210000000001</v>
       </c>
       <c r="G28" s="16" t="n">
-        <v>909.091</v>
+        <v>36.3636</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>1100</v>
+        <v>21.8182</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.02</t>
+          <t>0.002 / 0.035</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.02</t>
+          <t>0.0007 / 0.01225</t>
         </is>
       </c>
       <c r="K28" s="16" t="inlineStr">
         <is>
-          <t>1.4 / 0.15</t>
+          <t>0.0005 / 0.002</t>
         </is>
       </c>
       <c r="L28" s="16" t="inlineStr">
         <is>
-          <t>3.2 / 0.2</t>
+          <t>0.0005 / 0.002</t>
         </is>
       </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>55 / 18</t>
+          <t>0.02 / 0.65</t>
         </is>
       </c>
       <c r="N28" s="16" t="inlineStr">
         <is>
-          <t>4.9 / 4.2</t>
+          <t>0.0122647 / 0.244086</t>
         </is>
       </c>
       <c r="O28" s="16" t="inlineStr">
         <is>
-          <t>Vacuum arc remelting runs ~1,000-1,300 kWh/t on top of primary melting.</t>
+          <t>Scrap shredding and baling draws ~20-25 kWh per tonne of scrap; yard diesel for mobile handling ~3-5 L/t.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
         <is>
-          <t>Primary Melting</t>
+          <t>Sizing / Cutting / Screening</t>
         </is>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>ESR Remelting</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E29" s="16" t="n">
-        <v>3246.75</v>
+        <v>12.987</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>1500</v>
+        <v>4.54545</v>
       </c>
       <c r="G29" s="16" t="n">
-        <v>844.1559999999999</v>
+        <v>19.4805</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>1300</v>
+        <v>6.81818</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.015</t>
+          <t>0.008 / 0.02</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.015</t>
+          <t>0.0032 / 0.008</t>
         </is>
       </c>
       <c r="K29" s="16" t="inlineStr">
         <is>
-          <t>1.35 / 0.14</t>
+          <t>0.0005 / 0.0008</t>
         </is>
       </c>
       <c r="L29" s="16" t="inlineStr">
         <is>
-          <t>3.2 / 0.2</t>
+          <t>0.0005 / 0.0008</t>
         </is>
       </c>
       <c r="M29" s="16" t="inlineStr">
         <is>
-          <t>48 / 16</t>
+          <t>0.28 / 0.4</t>
         </is>
       </c>
       <c r="N29" s="16" t="inlineStr">
         <is>
-          <t>5.6 / 4.9</t>
+          <t>0.0596069 / 0.132654</t>
         </is>
       </c>
       <c r="O29" s="16" t="inlineStr">
         <is>
-          <t>Electroslag remelting runs ~1,200-1,600 kWh/t.</t>
+          <t>Sizing and screening: ~4-8 kWh/t and light mobile-plant diesel.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
         <is>
-          <t>Decarburization / Alloying</t>
+          <t>Bedding / Stacking / Stockyard</t>
         </is>
       </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
-          <t>AOD</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E30" s="16" t="n">
-        <v>194.805</v>
+        <v>15.5844</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>60</v>
+        <v>4.67532</v>
       </c>
       <c r="G30" s="16" t="n">
-        <v>129.87</v>
+        <v>6.49351</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>45</v>
+        <v>1.94805</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.04</t>
+          <t>0.01 / 0.008</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.04</t>
+          <t>0.004 / 0.0032</t>
         </is>
       </c>
       <c r="K30" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.08</t>
+          <t>0.0003 / 0.0003</t>
         </is>
       </c>
       <c r="L30" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.08</t>
+          <t>0.0003 / 0.0003</t>
         </is>
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>3.5 / 2</t>
+          <t>0.22 / 0.15</t>
         </is>
       </c>
       <c r="N30" s="16" t="inlineStr">
         <is>
-          <t>0.9 / 0.6</t>
+          <t>0.0708852 / 0.0502562</t>
         </is>
       </c>
       <c r="O30" s="16" t="inlineStr">
         <is>
-          <t>AOD needs little electricity of its own; oxygen, argon and nitrogen supply plus fume extraction come to ~40-60 kWh/t. Decarburisation CO2 left as in Grid 4.</t>
+          <t>Stockyard stacking and reclaiming: ~3-5 kWh/t; mobile plant diesel.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
         <is>
-          <t>Decarburization / Alloying</t>
+          <t>Proportioning / Charge Basket</t>
         </is>
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>VOD</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E31" s="16" t="n">
-        <v>454.545</v>
+        <v>7.79221</v>
       </c>
       <c r="F31" s="16" t="n">
-        <v>100</v>
+        <v>2.33766</v>
       </c>
       <c r="G31" s="16" t="n">
-        <v>259.74</v>
+        <v>15.5844</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>70</v>
+        <v>4.67532</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.035</t>
+          <t>0.001 / 0.002</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.035</t>
+          <t>0.001 / 0.002</t>
         </is>
       </c>
       <c r="K31" s="16" t="inlineStr">
         <is>
-          <t>0.22 / 0.09</t>
+          <t>0.0002 / 0.0002</t>
         </is>
       </c>
       <c r="L31" s="16" t="inlineStr">
         <is>
-          <t>0.22 / 0.09</t>
+          <t>0.0002 / 0.0002</t>
         </is>
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>6 / 3</t>
+          <t>0.1 / 0.18</t>
         </is>
       </c>
       <c r="N31" s="16" t="inlineStr">
         <is>
-          <t>1.2 / 0.9</t>
+          <t>0.0219291 / 0.0438582</t>
         </is>
       </c>
       <c r="O31" s="16" t="inlineStr">
         <is>
-          <t>VOD vacuum pumping and gas supply: ~60-100 kWh/t.</t>
+          <t>Charge-bucket make-up: cranes and weighing, ~2-4 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>Melt Shop</t>
+          <t>RMHS</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
         <is>
-          <t>Decarburization / Alloying</t>
+          <t>Internal Conveying / Furnace Feeding</t>
         </is>
       </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
-          <t>K-OBM-S</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E32" s="16" t="n">
-        <v>233.766</v>
+        <v>19.4805</v>
       </c>
       <c r="F32" s="16" t="n">
-        <v>70</v>
+        <v>4.87013</v>
       </c>
       <c r="G32" s="16" t="n">
-        <v>129.87</v>
+        <v>23.3766</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>50</v>
+        <v>5.84416</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
-          <t>0.1 / 0.06</t>
+          <t>0.0005 / 0.0008</t>
         </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>0.1 / 0.06</t>
+          <t>0.0005 / 0.0008</t>
         </is>
       </c>
       <c r="K32" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.08</t>
+          <t>0.0001 / 0.0001</t>
         </is>
       </c>
       <c r="L32" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.08</t>
+          <t>0.0001 / 0.0001</t>
         </is>
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>3 / 1.8</t>
+          <t>0.12 / 0.15</t>
         </is>
       </c>
       <c r="N32" s="16" t="inlineStr">
         <is>
-          <t>1.3 / 0.9</t>
+          <t>0.0242892 / 0.0318498</t>
         </is>
       </c>
       <c r="O32" s="16" t="inlineStr">
         <is>
-          <t>K-OBM-S: converter blowing, gas supply and fume system ~50-70 kWh/t.</t>
+          <t>Belt conveying is ~0.5-1 kWh per tonne per km; in-plant runs total ~3-6 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
@@ -11907,65 +11407,65 @@
       </c>
       <c r="C33" s="16" t="inlineStr">
         <is>
-          <t>Decarburization / Alloying</t>
+          <t>Scrap Prep / Charging</t>
         </is>
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>CLU</t>
+          <t>General (all types)</t>
         </is>
       </c>
       <c r="E33" s="16" t="n">
-        <v>207.792</v>
+        <v>12.987</v>
       </c>
       <c r="F33" s="16" t="n">
-        <v>65</v>
+        <v>4.54545</v>
       </c>
       <c r="G33" s="16" t="n">
-        <v>129.87</v>
+        <v>32.4675</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>48</v>
+        <v>11.3636</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.04</t>
+          <t>0.005 / 0.01</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.04</t>
+          <t>0.005 / 0.01</t>
         </is>
       </c>
       <c r="K33" s="16" t="inlineStr">
         <is>
-          <t>0.21 / 0.085</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="L33" s="16" t="inlineStr">
         <is>
-          <t>0.21 / 0.085</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="M33" s="16" t="inlineStr">
         <is>
-          <t>3.6 / 2.1</t>
+          <t>0.15 / 0.25</t>
         </is>
       </c>
       <c r="N33" s="16" t="inlineStr">
         <is>
-          <t>1 / 0.7</t>
+          <t>0.105649 / 0.219481</t>
         </is>
       </c>
       <c r="O33" s="16" t="inlineStr">
         <is>
-          <t>CLU: as AOD with steam dilution, ~50-65 kWh/t.</t>
+          <t>Scrap charging cranes and magnets: ~4-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
@@ -11974,65 +11474,65 @@
       </c>
       <c r="C34" s="16" t="inlineStr">
         <is>
-          <t>Secondary Refining / Homogenization</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Ladle Furnace (LF)</t>
+          <t>Electric Arc Furnace (EAF)</t>
         </is>
       </c>
       <c r="E34" s="16" t="n">
-        <v>454.545</v>
+        <v>2272.73</v>
       </c>
       <c r="F34" s="16" t="n">
-        <v>55</v>
+        <v>650</v>
       </c>
       <c r="G34" s="16" t="n">
-        <v>155.844</v>
+        <v>545.455</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>35</v>
+        <v>460</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.015</t>
+          <t>0.42 / 0.05</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.004</t>
+          <t>0.14 / 0.1</t>
         </is>
       </c>
       <c r="K34" s="16" t="inlineStr">
         <is>
-          <t>0.25 / 0.05</t>
+          <t>1.1 / 0.12</t>
         </is>
       </c>
       <c r="L34" s="16" t="inlineStr">
         <is>
-          <t>0.08 / 0.04</t>
+          <t>3.2 / 0.2</t>
         </is>
       </c>
       <c r="M34" s="16" t="inlineStr">
         <is>
-          <t>1.8 / 0.7</t>
+          <t>23 / 5.8</t>
         </is>
       </c>
       <c r="N34" s="16" t="inlineStr">
         <is>
-          <t>0.305143 / 0.197429</t>
+          <t>3.1 / 2.1</t>
         </is>
       </c>
       <c r="O34" s="16" t="inlineStr">
         <is>
-          <t>Ladle furnace arcing is ~30-50 kWh/t; trim-alloy additions ~0.04-0.08 tCO2e/t upstream.</t>
+          <t>Stainless EAF melts scrap at ~420-480 kWh/t; a virgin-heavy charge (ferroalloys, pig iron, DRI) needs more, ~600-700 kWh/t. Direct emissions from electrodes (1.2-3 kg/t), charge carbon and burners: ~0.10 tCO2/t on scrap (typical EAF ~102 kg/t), more on a carbon-rich virgin charge.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
@@ -12041,65 +11541,65 @@
       </c>
       <c r="C35" s="16" t="inlineStr">
         <is>
-          <t>Secondary Refining / Homogenization</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D35" s="16" t="inlineStr">
         <is>
-          <t>Inert Gas Stirring — Argon</t>
+          <t>Induction Furnace (IF)</t>
         </is>
       </c>
       <c r="E35" s="16" t="n">
-        <v>25.974</v>
+        <v>1428.57</v>
       </c>
       <c r="F35" s="16" t="n">
-        <v>12.987</v>
+        <v>750</v>
       </c>
       <c r="G35" s="16" t="n">
-        <v>12.987</v>
+        <v>454.545</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>6.49351</v>
+        <v>600</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
-          <t>0.005 / 0.003</t>
+          <t>0.02 / 0.01</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>0.005 / 0.003</t>
+          <t>0.02 / 0.01</t>
         </is>
       </c>
       <c r="K35" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.015</t>
+          <t>0.9 / 0.1</t>
         </is>
       </c>
       <c r="L35" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.015</t>
+          <t>3.2 / 0.2</t>
         </is>
       </c>
       <c r="M35" s="16" t="inlineStr">
         <is>
-          <t>0.15 / 0.08</t>
+          <t>18 / 4.5</t>
         </is>
       </c>
       <c r="N35" s="16" t="inlineStr">
         <is>
-          <t>0.136039 / 0.0769481</t>
+          <t>2.8 / 2.2</t>
         </is>
       </c>
       <c r="O35" s="16" t="inlineStr">
         <is>
-          <t>Argon stirring: gas supply energy only.</t>
+          <t>Induction furnaces melt scrap at ~550-650 kWh/t with negligible direct emissions.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
@@ -12108,65 +11608,65 @@
       </c>
       <c r="C36" s="16" t="inlineStr">
         <is>
-          <t>Secondary Refining / Homogenization</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
-          <t>Inert Gas Stirring — Nitrogen</t>
+          <t>Integrated BF/Converter</t>
         </is>
       </c>
       <c r="E36" s="16" t="n">
-        <v>19.4805</v>
+        <v>454.545</v>
       </c>
       <c r="F36" s="16" t="n">
-        <v>9.740259999999999</v>
+        <v>300</v>
       </c>
       <c r="G36" s="16" t="n">
-        <v>10.3896</v>
+        <v>64.93510000000001</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>5.1948</v>
+        <v>65</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0025</t>
+          <t>1.8 / 0.05</t>
         </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0025</t>
+          <t>1.8 / 0.05</t>
         </is>
       </c>
       <c r="K36" s="16" t="inlineStr">
         <is>
-          <t>0.018 / 0.009</t>
+          <t>1.5 / 0.15</t>
         </is>
       </c>
       <c r="L36" s="16" t="inlineStr">
         <is>
-          <t>0.018 / 0.009</t>
+          <t>1.8 / 0.2</t>
         </is>
       </c>
       <c r="M36" s="16" t="inlineStr">
         <is>
-          <t>0.1 / 0.05</t>
+          <t>32 / 5</t>
         </is>
       </c>
       <c r="N36" s="16" t="inlineStr">
         <is>
-          <t>0.106494 / 0.0633442</t>
+          <t>19 / 3.5</t>
         </is>
       </c>
       <c r="O36" s="16" t="inlineStr">
         <is>
-          <t>Nitrogen stirring: gas supply energy only.</t>
+          <t>Integrated BF/converter: Scope 1 already carries the iron-making reductant (~1.8 tCO2/t hot metal), so Scope 3 carries only the alloy units; electricity for blast, oxygen and auxiliaries ~250-350 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="16" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
@@ -12175,65 +11675,65 @@
       </c>
       <c r="C37" s="16" t="inlineStr">
         <is>
-          <t>Secondary Refining / Homogenization</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>VD / RH Degasser</t>
+          <t>Vacuum / Special Induction (VIM)</t>
         </is>
       </c>
       <c r="E37" s="16" t="n">
-        <v>584.4160000000001</v>
+        <v>2857.14</v>
       </c>
       <c r="F37" s="16" t="n">
-        <v>45</v>
+        <v>1000</v>
       </c>
       <c r="G37" s="16" t="n">
-        <v>233.766</v>
+        <v>714.2859999999999</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>30</v>
+        <v>800</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.007</t>
+          <t>0.02 / 0.015</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.007</t>
+          <t>0.02 / 0.015</t>
         </is>
       </c>
       <c r="K37" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.02</t>
+          <t>1.3 / 0.12</t>
         </is>
       </c>
       <c r="L37" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.02</t>
+          <t>3.2 / 0.2</t>
         </is>
       </c>
       <c r="M37" s="16" t="inlineStr">
         <is>
-          <t>4.5 / 1.8</t>
+          <t>45 / 15</t>
         </is>
       </c>
       <c r="N37" s="16" t="inlineStr">
         <is>
-          <t>0.340571 / 0.233</t>
+          <t>3.8 / 3.1</t>
         </is>
       </c>
       <c r="O37" s="16" t="inlineStr">
         <is>
-          <t>VD/RH degassing with mechanical pumps: ~30-45 kWh/t.</t>
+          <t>Vacuum induction melting runs ~800-1,000 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="16" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
@@ -12242,65 +11742,65 @@
       </c>
       <c r="C38" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
-          <t>Curved Mold Caster</t>
+          <t>Vacuum Arc Remelting (VAR)</t>
         </is>
       </c>
       <c r="E38" s="16" t="n">
-        <v>129.87</v>
+        <v>3636.36</v>
       </c>
       <c r="F38" s="16" t="n">
-        <v>35</v>
+        <v>1300</v>
       </c>
       <c r="G38" s="16" t="n">
-        <v>77.9221</v>
+        <v>909.091</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>28</v>
+        <v>1100</v>
       </c>
       <c r="I38" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.012</t>
+          <t>0.03 / 0.02</t>
         </is>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>0.008 / 0.0048</t>
+          <t>0.03 / 0.02</t>
         </is>
       </c>
       <c r="K38" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.015</t>
+          <t>1.4 / 0.15</t>
         </is>
       </c>
       <c r="L38" s="16" t="inlineStr">
         <is>
-          <t>0.021 / 0.0105</t>
+          <t>3.2 / 0.2</t>
         </is>
       </c>
       <c r="M38" s="16" t="inlineStr">
         <is>
-          <t>0.9 / 0.5</t>
+          <t>55 / 18</t>
         </is>
       </c>
       <c r="N38" s="16" t="inlineStr">
         <is>
-          <t>0.268857 / 0.186514</t>
+          <t>4.9 / 4.2</t>
         </is>
       </c>
       <c r="O38" s="16" t="inlineStr">
         <is>
-          <t>Slab casters use ~20-35 kWh/t including the water system; tundish preheating and torch cutting are small.</t>
+          <t>Vacuum arc remelting runs ~1,000-1,300 kWh/t on top of primary melting.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
@@ -12309,65 +11809,65 @@
       </c>
       <c r="C39" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Primary Melting</t>
         </is>
       </c>
       <c r="D39" s="16" t="inlineStr">
         <is>
-          <t>Vertical Continuous Caster</t>
+          <t>ESR Remelting</t>
         </is>
       </c>
       <c r="E39" s="16" t="n">
-        <v>155.844</v>
+        <v>3246.75</v>
       </c>
       <c r="F39" s="16" t="n">
-        <v>40</v>
+        <v>1500</v>
       </c>
       <c r="G39" s="16" t="n">
-        <v>90.9091</v>
+        <v>844.1559999999999</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>32</v>
+        <v>1300</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
-          <t>0.022 / 0.013</t>
+          <t>0.02 / 0.015</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>0.0088 / 0.0052</t>
+          <t>0.02 / 0.015</t>
         </is>
       </c>
       <c r="K39" s="16" t="inlineStr">
         <is>
-          <t>0.032 / 0.016</t>
+          <t>1.35 / 0.14</t>
         </is>
       </c>
       <c r="L39" s="16" t="inlineStr">
         <is>
-          <t>0.0224 / 0.0112</t>
+          <t>3.2 / 0.2</t>
         </is>
       </c>
       <c r="M39" s="16" t="inlineStr">
         <is>
-          <t>1 / 0.55</t>
+          <t>48 / 16</t>
         </is>
       </c>
       <c r="N39" s="16" t="inlineStr">
         <is>
-          <t>0.301143 / 0.208057</t>
+          <t>5.6 / 4.9</t>
         </is>
       </c>
       <c r="O39" s="16" t="inlineStr">
         <is>
-          <t>Vertical caster: as the curved-mould caster, slightly more.</t>
+          <t>Electroslag remelting runs ~1,200-1,600 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
@@ -12376,65 +11876,65 @@
       </c>
       <c r="C40" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Decarburization / Alloying</t>
         </is>
       </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
-          <t>Thin Slab Casting</t>
+          <t>AOD</t>
         </is>
       </c>
       <c r="E40" s="16" t="n">
-        <v>181.818</v>
+        <v>194.805</v>
       </c>
       <c r="F40" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="G40" s="16" t="n">
+        <v>129.87</v>
+      </c>
+      <c r="H40" s="16" t="n">
         <v>45</v>
       </c>
-      <c r="G40" s="16" t="n">
-        <v>103.896</v>
-      </c>
-      <c r="H40" s="16" t="n">
-        <v>36</v>
-      </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
-          <t>0.018 / 0.011</t>
+          <t>0.06 / 0.04</t>
         </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>0.0072 / 0.0044</t>
+          <t>0.09 / 0.05</t>
         </is>
       </c>
       <c r="K40" s="16" t="inlineStr">
         <is>
-          <t>0.028 / 0.014</t>
+          <t>0.2 / 0.08</t>
         </is>
       </c>
       <c r="L40" s="16" t="inlineStr">
         <is>
-          <t>0.0196 / 0.0098</t>
+          <t>0.2 / 0.08</t>
         </is>
       </c>
       <c r="M40" s="16" t="inlineStr">
         <is>
-          <t>0.85 / 0.48</t>
+          <t>3.5 / 2</t>
         </is>
       </c>
       <c r="N40" s="16" t="inlineStr">
         <is>
-          <t>0.290571 / 0.208171</t>
+          <t>0.9 / 0.6</t>
         </is>
       </c>
       <c r="O40" s="16" t="inlineStr">
         <is>
-          <t>Thin-slab casting: ~35-45 kWh/t with the direct-link furnace excluded.</t>
+          <t>AOD needs little electricity of its own; oxygen, argon and nitrogen supply plus fume extraction come to ~40-60 kWh/t. Decarburising from ~1.5-2.5% C (more on a high-carbon ferrochrome charge) to &lt;0.05% C releases ~0.05-0.09 tCO2/t.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="16" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
@@ -12443,65 +11943,65 @@
       </c>
       <c r="C41" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Decarburization / Alloying</t>
         </is>
       </c>
       <c r="D41" s="16" t="inlineStr">
         <is>
-          <t>Submerged Entry Nozzle (SEN)</t>
+          <t>VOD</t>
         </is>
       </c>
       <c r="E41" s="16" t="n">
-        <v>6.49351</v>
+        <v>454.545</v>
       </c>
       <c r="F41" s="16" t="n">
-        <v>3.24675</v>
+        <v>100</v>
       </c>
       <c r="G41" s="16" t="n">
-        <v>3.8961</v>
+        <v>259.74</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>1.94805</v>
+        <v>70</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0008</t>
+          <t>0.05 / 0.035</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0008</t>
+          <t>0.05 / 0.035</t>
         </is>
       </c>
       <c r="K41" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.008</t>
+          <t>0.22 / 0.09</t>
         </is>
       </c>
       <c r="L41" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.008</t>
+          <t>0.22 / 0.09</t>
         </is>
       </c>
       <c r="M41" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.02</t>
+          <t>6 / 3</t>
         </is>
       </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
-          <t>0.0295455 / 0.0212987</t>
+          <t>1.2 / 0.9</t>
         </is>
       </c>
       <c r="O41" s="16" t="inlineStr">
         <is>
-          <t>SEN: a refractory practice, not a load of its own.</t>
+          <t>VOD vacuum pumping and gas supply: ~60-100 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="16" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
@@ -12510,65 +12010,65 @@
       </c>
       <c r="C42" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Decarburization / Alloying</t>
         </is>
       </c>
       <c r="D42" s="16" t="inlineStr">
         <is>
-          <t>Argon Shrouding</t>
+          <t>K-OBM-S</t>
         </is>
       </c>
       <c r="E42" s="16" t="n">
-        <v>10.3896</v>
+        <v>233.766</v>
       </c>
       <c r="F42" s="16" t="n">
-        <v>5.1948</v>
+        <v>70</v>
       </c>
       <c r="G42" s="16" t="n">
-        <v>5.1948</v>
+        <v>129.87</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>2.5974</v>
+        <v>50</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0003</t>
+          <t>0.1 / 0.06</t>
         </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0003</t>
+          <t>0.1 / 0.06</t>
         </is>
       </c>
       <c r="K42" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.01</t>
+          <t>0.2 / 0.08</t>
         </is>
       </c>
       <c r="L42" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.01</t>
+          <t>0.2 / 0.08</t>
         </is>
       </c>
       <c r="M42" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.025</t>
+          <t>3 / 1.8</t>
         </is>
       </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
-          <t>0.0276299 / 0.0147078</t>
+          <t>1.3 / 0.9</t>
         </is>
       </c>
       <c r="O42" s="16" t="inlineStr">
         <is>
-          <t>Argon shrouding: gas supply energy only.</t>
+          <t>K-OBM-S: converter blowing, gas supply and fume system ~50-70 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="16" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
@@ -12577,65 +12077,65 @@
       </c>
       <c r="C43" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Decarburization / Alloying</t>
         </is>
       </c>
       <c r="D43" s="16" t="inlineStr">
         <is>
-          <t>Mold Electromagnetic Stirring (MEMS)</t>
+          <t>CLU</t>
         </is>
       </c>
       <c r="E43" s="16" t="n">
-        <v>77.9221</v>
+        <v>207.792</v>
       </c>
       <c r="F43" s="16" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="G43" s="16" t="n">
-        <v>45.4545</v>
+        <v>129.87</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0007</t>
+          <t>0.06 / 0.04</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0007</t>
+          <t>0.09 / 0.05</t>
         </is>
       </c>
       <c r="K43" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.005</t>
+          <t>0.21 / 0.085</t>
         </is>
       </c>
       <c r="L43" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.005</t>
+          <t>0.21 / 0.085</t>
         </is>
       </c>
       <c r="M43" s="16" t="inlineStr">
         <is>
-          <t>0.45 / 0.25</t>
+          <t>3.6 / 2.1</t>
         </is>
       </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
-          <t>0.0466571 / 0.0341</t>
+          <t>1 / 0.7</t>
         </is>
       </c>
       <c r="O43" s="16" t="inlineStr">
         <is>
-          <t>Mould EMS draws ~5-10 kWh/t.</t>
+          <t>CLU: as AOD with steam dilution, ~50-65 kWh/t; same decarburisation CO2.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="16" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
@@ -12644,65 +12144,65 @@
       </c>
       <c r="C44" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Secondary Refining / Homogenization</t>
         </is>
       </c>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Soft Reduction</t>
+          <t>Ladle Furnace (LF)</t>
         </is>
       </c>
       <c r="E44" s="16" t="n">
-        <v>38.961</v>
+        <v>454.545</v>
       </c>
       <c r="F44" s="16" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="G44" s="16" t="n">
-        <v>23.3766</v>
+        <v>155.844</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
-          <t>0.0008 / 0.0005</t>
+          <t>0.03 / 0.015</t>
         </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.0008 / 0.0005</t>
+          <t>0.006 / 0.004</t>
         </is>
       </c>
       <c r="K44" s="16" t="inlineStr">
         <is>
-          <t>0.008 / 0.004</t>
+          <t>0.25 / 0.05</t>
         </is>
       </c>
       <c r="L44" s="16" t="inlineStr">
         <is>
-          <t>0.008 / 0.004</t>
+          <t>0.08 / 0.04</t>
         </is>
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.12</t>
+          <t>1.8 / 0.7</t>
         </is>
       </c>
       <c r="N44" s="16" t="inlineStr">
         <is>
-          <t>0.0286857 / 0.0197286</t>
+          <t>0.305143 / 0.197429</t>
         </is>
       </c>
       <c r="O44" s="16" t="inlineStr">
         <is>
-          <t>Soft reduction: segment actuation, ~3-5 kWh/t.</t>
+          <t>Ladle furnace arcing is ~30-50 kWh/t; trim-alloy additions ~0.04-0.08 tCO2e/t upstream.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
@@ -12711,744 +12211,744 @@
       </c>
       <c r="C45" s="16" t="inlineStr">
         <is>
-          <t>Continuous Casting (CCM)</t>
+          <t>Secondary Refining / Homogenization</t>
         </is>
       </c>
       <c r="D45" s="16" t="inlineStr">
         <is>
-          <t>Dynamic Secondary / Air-Mist Cooling</t>
+          <t>Inert Gas Stirring — Argon</t>
         </is>
       </c>
       <c r="E45" s="16" t="n">
-        <v>51.9481</v>
+        <v>25.974</v>
       </c>
       <c r="F45" s="16" t="n">
-        <v>8</v>
+        <v>12.987</v>
       </c>
       <c r="G45" s="16" t="n">
-        <v>31.1688</v>
+        <v>12.987</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>6</v>
+        <v>6.49351</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0003</t>
+          <t>0.005 / 0.003</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0003</t>
+          <t>0.005 / 0.003</t>
         </is>
       </c>
       <c r="K45" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.003</t>
+          <t>0.03 / 0.015</t>
         </is>
       </c>
       <c r="L45" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.003</t>
+          <t>0.03 / 0.015</t>
         </is>
       </c>
       <c r="M45" s="16" t="inlineStr">
         <is>
-          <t>0.3 / 0.18</t>
+          <t>0.15 / 0.08</t>
         </is>
       </c>
       <c r="N45" s="16" t="inlineStr">
         <is>
-          <t>0.0377286 / 0.0269571</t>
+          <t>0.136039 / 0.0769481</t>
         </is>
       </c>
       <c r="O45" s="16" t="inlineStr">
         <is>
-          <t>Air-mist cooling: spray pumps, ~5-10 kWh/t.</t>
+          <t>Argon stirring: gas supply energy only.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C46" s="16" t="inlineStr">
         <is>
-          <t>Slab Prep / Surface Grinding</t>
+          <t>Secondary Refining / Homogenization</t>
         </is>
       </c>
       <c r="D46" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Inert Gas Stirring — Nitrogen</t>
         </is>
       </c>
       <c r="E46" s="16" t="n">
-        <v>32.4675</v>
+        <v>19.4805</v>
       </c>
       <c r="F46" s="16" t="n">
-        <v>8.11688</v>
+        <v>9.740259999999999</v>
       </c>
       <c r="G46" s="16" t="n">
-        <v>28.5714</v>
+        <v>10.3896</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>7.14286</v>
+        <v>5.1948</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0025</t>
+          <t>0.004 / 0.0025</t>
         </is>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0025</t>
+          <t>0.004 / 0.0025</t>
         </is>
       </c>
       <c r="K46" s="16" t="inlineStr">
         <is>
-          <t>0.005 / 0.004</t>
+          <t>0.018 / 0.009</t>
         </is>
       </c>
       <c r="L46" s="16" t="inlineStr">
         <is>
-          <t>0.005 / 0.004</t>
+          <t>0.018 / 0.009</t>
         </is>
       </c>
       <c r="M46" s="16" t="inlineStr">
         <is>
-          <t>0.35 / 0.3</t>
+          <t>0.1 / 0.05</t>
         </is>
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>0.0827922 / 0.0703571</t>
+          <t>0.106494 / 0.0633442</t>
         </is>
       </c>
       <c r="O46" s="16" t="inlineStr">
         <is>
-          <t>Slab grinding: ~6-10 kWh/t.</t>
+          <t>Nitrogen stirring: gas supply energy only.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C47" s="16" t="inlineStr">
         <is>
-          <t>Reheating in Furnace</t>
+          <t>Secondary Refining / Homogenization</t>
         </is>
       </c>
       <c r="D47" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>VD / RH Degasser</t>
         </is>
       </c>
       <c r="E47" s="16" t="n">
-        <v>19.4805</v>
+        <v>584.4160000000001</v>
       </c>
       <c r="F47" s="16" t="n">
-        <v>7.79221</v>
+        <v>45</v>
       </c>
       <c r="G47" s="16" t="n">
-        <v>18.1818</v>
+        <v>233.766</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>7.27273</v>
+        <v>30</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
-          <t>0.095 / 0.085</t>
+          <t>0.01 / 0.007</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>0.075 / 0.07</t>
+          <t>0.01 / 0.007</t>
         </is>
       </c>
       <c r="K47" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.05 / 0.02</t>
         </is>
       </c>
       <c r="L47" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.05 / 0.02</t>
         </is>
       </c>
       <c r="M47" s="16" t="inlineStr">
         <is>
-          <t>2.8 / 2.5</t>
+          <t>4.5 / 1.8</t>
         </is>
       </c>
       <c r="N47" s="16" t="inlineStr">
         <is>
-          <t>1.36734 / 1.27618</t>
+          <t>0.340571 / 0.233</t>
         </is>
       </c>
       <c r="O47" s="16" t="inlineStr">
         <is>
-          <t>Walking-beam reheating burns ~1.2-1.5 GJ/t of gas for stainless; fans ~5-10 kWh/t.</t>
+          <t>VD/RH degassing with mechanical pumps: ~30-45 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C48" s="16" t="inlineStr">
         <is>
-          <t>High Pressure Hydraulic Descaling</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D48" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Curved Mold Caster</t>
         </is>
       </c>
       <c r="E48" s="16" t="n">
-        <v>25.974</v>
+        <v>129.87</v>
       </c>
       <c r="F48" s="16" t="n">
-        <v>7.79221</v>
+        <v>35</v>
       </c>
       <c r="G48" s="16" t="n">
-        <v>23.3766</v>
+        <v>77.9221</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>7.01299</v>
+        <v>28</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.02 / 0.012</t>
         </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.008 / 0.0048</t>
         </is>
       </c>
       <c r="K48" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.03 / 0.015</t>
         </is>
       </c>
       <c r="L48" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.021 / 0.0105</t>
         </is>
       </c>
       <c r="M48" s="16" t="inlineStr">
         <is>
-          <t>0.18 / 0.16</t>
+          <t>0.9 / 0.5</t>
         </is>
       </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
-          <t>0.0459091 / 0.0431039</t>
+          <t>0.268857 / 0.186514</t>
         </is>
       </c>
       <c r="O48" s="16" t="inlineStr">
         <is>
-          <t>HP descaling pumps: ~6-10 kWh/t.</t>
+          <t>Slab casters use ~20-35 kWh/t including the water system; tundish preheating and torch cutting are small.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C49" s="16" t="inlineStr">
         <is>
-          <t>Roughing Rolling Mill</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D49" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Vertical Continuous Caster</t>
         </is>
       </c>
       <c r="E49" s="16" t="n">
-        <v>116.883</v>
+        <v>155.844</v>
       </c>
       <c r="F49" s="16" t="n">
-        <v>35.0649</v>
+        <v>40</v>
       </c>
       <c r="G49" s="16" t="n">
-        <v>103.896</v>
+        <v>90.9091</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>31.1688</v>
+        <v>32</v>
       </c>
       <c r="I49" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.022 / 0.013</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.0088 / 0.0052</t>
         </is>
       </c>
       <c r="K49" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0035</t>
+          <t>0.032 / 0.016</t>
         </is>
       </c>
       <c r="L49" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0035</t>
+          <t>0.0224 / 0.0112</t>
         </is>
       </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>0.55 / 0.48</t>
+          <t>1 / 0.55</t>
         </is>
       </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
-          <t>0.161948 / 0.144351</t>
+          <t>0.301143 / 0.208057</t>
         </is>
       </c>
       <c r="O49" s="16" t="inlineStr">
         <is>
-          <t>Roughing mill: ~30-40 kWh/t.</t>
+          <t>Vertical caster: as the curved-mould caster, slightly more.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="n">
+        <v>26</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Melt Shop</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>Continuous Casting (CCM)</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Thin Slab Casting</t>
+        </is>
+      </c>
+      <c r="E50" s="16" t="n">
+        <v>181.818</v>
+      </c>
+      <c r="F50" s="16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G50" s="16" t="n">
+        <v>103.896</v>
+      </c>
+      <c r="H50" s="16" t="n">
         <v>36</v>
       </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>Hot Rolling</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>Crop Shearing / Intermediate Heating</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="inlineStr">
-        <is>
-          <t>General (all types)</t>
-        </is>
-      </c>
-      <c r="E50" s="16" t="n">
-        <v>25.974</v>
-      </c>
-      <c r="F50" s="16" t="n">
-        <v>7.79221</v>
-      </c>
-      <c r="G50" s="16" t="n">
-        <v>23.3766</v>
-      </c>
-      <c r="H50" s="16" t="n">
-        <v>7.01299</v>
-      </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.013</t>
+          <t>0.018 / 0.011</t>
         </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>0.00525 / 0.00455</t>
+          <t>0.0072 / 0.0044</t>
         </is>
       </c>
       <c r="K50" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0035</t>
+          <t>0.028 / 0.014</t>
         </is>
       </c>
       <c r="L50" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0035</t>
+          <t>0.0196 / 0.0098</t>
         </is>
       </c>
       <c r="M50" s="16" t="inlineStr">
         <is>
-          <t>0.65 / 0.58</t>
+          <t>0.85 / 0.48</t>
         </is>
       </c>
       <c r="N50" s="16" t="inlineStr">
         <is>
-          <t>0.121802 / 0.106497</t>
+          <t>0.290571 / 0.208171</t>
         </is>
       </c>
       <c r="O50" s="16" t="inlineStr">
         <is>
-          <t>Crop shear and coil box / edge heating: ~5-10 kWh/t and little fuel.</t>
+          <t>Thin-slab casting: ~35-45 kWh/t with the direct-link furnace excluded.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C51" s="16" t="inlineStr">
         <is>
-          <t>Finishing Rolling Train</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Submerged Entry Nozzle (SEN)</t>
         </is>
       </c>
       <c r="E51" s="16" t="n">
-        <v>181.818</v>
+        <v>6.49351</v>
       </c>
       <c r="F51" s="16" t="n">
-        <v>50.9091</v>
+        <v>3.24675</v>
       </c>
       <c r="G51" s="16" t="n">
-        <v>162.338</v>
+        <v>3.8961</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>45.4545</v>
+        <v>1.94805</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.001 / 0.0008</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.001 / 0.0008</t>
         </is>
       </c>
       <c r="K51" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.005</t>
+          <t>0.015 / 0.008</t>
         </is>
       </c>
       <c r="L51" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.005</t>
+          <t>0.015 / 0.008</t>
         </is>
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>0.85 / 0.75</t>
+          <t>0.03 / 0.02</t>
         </is>
       </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
-          <t>0.218987 / 0.195779</t>
+          <t>0.0295455 / 0.0212987</t>
         </is>
       </c>
       <c r="O51" s="16" t="inlineStr">
         <is>
-          <t>Finishing train: ~45-60 kWh/t for stainless strip.</t>
+          <t>SEN: a refractory practice, not a load of its own.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C52" s="16" t="inlineStr">
         <is>
-          <t>Controlled Cooling</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D52" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Argon Shrouding</t>
         </is>
       </c>
       <c r="E52" s="16" t="n">
-        <v>32.4675</v>
+        <v>10.3896</v>
       </c>
       <c r="F52" s="16" t="n">
-        <v>6.49351</v>
+        <v>5.1948</v>
       </c>
       <c r="G52" s="16" t="n">
-        <v>28.5714</v>
+        <v>5.1948</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>5.71429</v>
+        <v>2.5974</v>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.0005 / 0.0003</t>
         </is>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.0005 / 0.0003</t>
         </is>
       </c>
       <c r="K52" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.02 / 0.01</t>
         </is>
       </c>
       <c r="L52" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.02 / 0.01</t>
         </is>
       </c>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.18</t>
+          <t>0.05 / 0.025</t>
         </is>
       </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
-          <t>0.0323052 / 0.0277143</t>
+          <t>0.0276299 / 0.0147078</t>
         </is>
       </c>
       <c r="O52" s="16" t="inlineStr">
         <is>
-          <t>Laminar cooling pumps: ~5-8 kWh/t.</t>
+          <t>Argon shrouding: gas supply energy only.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Hot Rolling</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C53" s="16" t="inlineStr">
         <is>
-          <t>Coiling or Plate Shearing</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D53" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Mold Electromagnetic Stirring (MEMS)</t>
         </is>
       </c>
       <c r="E53" s="16" t="n">
-        <v>38.961</v>
+        <v>77.9221</v>
       </c>
       <c r="F53" s="16" t="n">
-        <v>7.01299</v>
+        <v>8</v>
       </c>
       <c r="G53" s="16" t="n">
-        <v>35.0649</v>
+        <v>45.4545</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>6.31169</v>
+        <v>6</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.001 / 0.0007</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.001 / 0.0007</t>
         </is>
       </c>
       <c r="K53" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.01 / 0.005</t>
         </is>
       </c>
       <c r="L53" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.01 / 0.005</t>
         </is>
       </c>
       <c r="M53" s="16" t="inlineStr">
         <is>
-          <t>0.15 / 0.13</t>
+          <t>0.45 / 0.25</t>
         </is>
       </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
-          <t>0.0431039 / 0.0387935</t>
+          <t>0.0466571 / 0.0341</t>
         </is>
       </c>
       <c r="O53" s="16" t="inlineStr">
         <is>
-          <t>Down-coiler or plate shear: ~5-8 kWh/t.</t>
+          <t>Mould EMS draws ~5-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C54" s="16" t="inlineStr">
         <is>
-          <t>Solution Annealing</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D54" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Soft Reduction</t>
         </is>
       </c>
       <c r="E54" s="16" t="n">
         <v>38.961</v>
       </c>
       <c r="F54" s="16" t="n">
-        <v>25.3247</v>
+        <v>4</v>
       </c>
       <c r="G54" s="16" t="n">
-        <v>36.3636</v>
+        <v>23.3766</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>23.6364</v>
+        <v>3</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.055</t>
+          <t>0.0008 / 0.0005</t>
         </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>0.054 / 0.0495</t>
+          <t>0.0008 / 0.0005</t>
         </is>
       </c>
       <c r="K54" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.014</t>
+          <t>0.008 / 0.004</t>
         </is>
       </c>
       <c r="L54" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.014</t>
+          <t>0.008 / 0.004</t>
         </is>
       </c>
       <c r="M54" s="16" t="inlineStr">
         <is>
-          <t>1.6 / 1.45</t>
+          <t>0.2 / 0.12</t>
         </is>
       </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
-          <t>1.05545 / 0.969019</t>
+          <t>0.0286857 / 0.0197286</t>
         </is>
       </c>
       <c r="O54" s="16" t="inlineStr">
         <is>
-          <t>Gas-fired solution annealing: ~0.8-1.1 GJ/t fuel, ~20-30 kWh/t.</t>
+          <t>Soft reduction: segment actuation, ~3-5 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Melt Shop</t>
         </is>
       </c>
       <c r="C55" s="16" t="inlineStr">
         <is>
-          <t>Subcritical Annealing</t>
+          <t>Continuous Casting (CCM)</t>
         </is>
       </c>
       <c r="D55" s="16" t="inlineStr">
         <is>
-          <t>General (all types)</t>
+          <t>Dynamic Secondary / Air-Mist Cooling</t>
         </is>
       </c>
       <c r="E55" s="16" t="n">
-        <v>23.3766</v>
+        <v>51.9481</v>
       </c>
       <c r="F55" s="16" t="n">
-        <v>15.1948</v>
+        <v>8</v>
       </c>
       <c r="G55" s="16" t="n">
-        <v>20.7792</v>
+        <v>31.1688</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>13.5065</v>
+        <v>6</v>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
-          <t>0.035 / 0.032</t>
+          <t>0.0005 / 0.0003</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>0.0315 / 0.0288</t>
+          <t>0.0005 / 0.0003</t>
         </is>
       </c>
       <c r="K55" s="16" t="inlineStr">
         <is>
-          <t>0.009 / 0.008</t>
+          <t>0.006 / 0.003</t>
         </is>
       </c>
       <c r="L55" s="16" t="inlineStr">
         <is>
-          <t>0.009 / 0.008</t>
+          <t>0.006 / 0.003</t>
         </is>
       </c>
       <c r="M55" s="16" t="inlineStr">
         <is>
-          <t>0.95 / 0.85</t>
+          <t>0.3 / 0.18</t>
         </is>
       </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
-          <t>0.617201 / 0.562909</t>
+          <t>0.0377286 / 0.0269571</t>
         </is>
       </c>
       <c r="O55" s="16" t="inlineStr">
         <is>
-          <t>Subcritical anneal: lower soak temperature.</t>
+          <t>Air-mist cooling: spray pumps, ~5-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C56" s="16" t="inlineStr">
         <is>
-          <t>Full Annealing / Tempering</t>
+          <t>Slab Prep / Surface Grinding</t>
         </is>
       </c>
       <c r="D56" s="16" t="inlineStr">
@@ -13460,62 +12960,62 @@
         <v>32.4675</v>
       </c>
       <c r="F56" s="16" t="n">
-        <v>21.1039</v>
+        <v>8.11688</v>
       </c>
       <c r="G56" s="16" t="n">
         <v>28.5714</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>18.5714</v>
+        <v>7.14286</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.045</t>
+          <t>0.003 / 0.0025</t>
         </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.045 / 0.0405</t>
+          <t>0.003 / 0.0025</t>
         </is>
       </c>
       <c r="K56" s="16" t="inlineStr">
         <is>
-          <t>0.012 / 0.011</t>
+          <t>0.005 / 0.004</t>
         </is>
       </c>
       <c r="L56" s="16" t="inlineStr">
         <is>
-          <t>0.012 / 0.011</t>
+          <t>0.005 / 0.004</t>
         </is>
       </c>
       <c r="M56" s="16" t="inlineStr">
         <is>
-          <t>1.35 / 1.2</t>
+          <t>0.35 / 0.3</t>
         </is>
       </c>
       <c r="N56" s="16" t="inlineStr">
         <is>
-          <t>0.879545 / 0.790071</t>
+          <t>0.0827922 / 0.0703571</t>
         </is>
       </c>
       <c r="O56" s="16" t="inlineStr">
         <is>
-          <t>Full anneal / temper: batch furnace.</t>
+          <t>Slab grinding: ~6-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C57" s="16" t="inlineStr">
         <is>
-          <t>Bright Annealing</t>
+          <t>Reheating in Furnace</t>
         </is>
       </c>
       <c r="D57" s="16" t="inlineStr">
@@ -13524,65 +13024,65 @@
         </is>
       </c>
       <c r="E57" s="16" t="n">
-        <v>58.4416</v>
+        <v>19.4805</v>
       </c>
       <c r="F57" s="16" t="n">
-        <v>46.7532</v>
+        <v>7.79221</v>
       </c>
       <c r="G57" s="16" t="n">
-        <v>51.9481</v>
+        <v>18.1818</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>41.5584</v>
+        <v>7.27273</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
-          <t>0.055 / 0.05</t>
+          <t>0.095 / 0.085</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.044 / 0.04</t>
+          <t>0.075 / 0.07</t>
         </is>
       </c>
       <c r="K57" s="16" t="inlineStr">
         <is>
-          <t>0.025 / 0.022</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="L57" s="16" t="inlineStr">
         <is>
-          <t>0.025 / 0.022</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="M57" s="16" t="inlineStr">
         <is>
-          <t>1.9 / 1.7</t>
+          <t>2.8 / 2.5</t>
         </is>
       </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
-          <t>0.954026 / 0.863896</t>
+          <t>1.36734 / 1.27618</t>
         </is>
       </c>
       <c r="O57" s="16" t="inlineStr">
         <is>
-          <t>Bright annealing in hydrogen / cracked ammonia.</t>
+          <t>Walking-beam reheating burns ~1.2-1.5 GJ/t of gas for stainless; fans ~5-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C58" s="16" t="inlineStr">
         <is>
-          <t>Open Annealing / Pickling</t>
+          <t>High Pressure Hydraulic Descaling</t>
         </is>
       </c>
       <c r="D58" s="16" t="inlineStr">
@@ -13591,65 +13091,65 @@
         </is>
       </c>
       <c r="E58" s="16" t="n">
-        <v>45.4545</v>
+        <v>25.974</v>
       </c>
       <c r="F58" s="16" t="n">
-        <v>29.5455</v>
+        <v>7.79221</v>
       </c>
       <c r="G58" s="16" t="n">
-        <v>41.5584</v>
+        <v>23.3766</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>27.013</v>
+        <v>7.01299</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.055</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>0.054 / 0.0495</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="K58" s="16" t="inlineStr">
         <is>
-          <t>0.04 / 0.036</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="L58" s="16" t="inlineStr">
         <is>
-          <t>0.04 / 0.036</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="M58" s="16" t="inlineStr">
         <is>
-          <t>1.7 / 1.55</t>
+          <t>0.18 / 0.16</t>
         </is>
       </c>
       <c r="N58" s="16" t="inlineStr">
         <is>
-          <t>1.07065 / 0.981175</t>
+          <t>0.0459091 / 0.0431039</t>
         </is>
       </c>
       <c r="O58" s="16" t="inlineStr">
         <is>
-          <t>Open annealing with pickling.</t>
+          <t>HP descaling pumps: ~6-10 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C59" s="16" t="inlineStr">
         <is>
-          <t>Continuous Strand / Tube Annealing</t>
+          <t>Roughing Rolling Mill</t>
         </is>
       </c>
       <c r="D59" s="16" t="inlineStr">
@@ -13658,65 +13158,65 @@
         </is>
       </c>
       <c r="E59" s="16" t="n">
-        <v>25.974</v>
+        <v>116.883</v>
       </c>
       <c r="F59" s="16" t="n">
-        <v>16.8831</v>
+        <v>35.0649</v>
       </c>
       <c r="G59" s="16" t="n">
-        <v>23.3766</v>
+        <v>103.896</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>15.1948</v>
+        <v>31.1688</v>
       </c>
       <c r="I59" s="16" t="inlineStr">
         <is>
-          <t>0.04 / 0.036</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>0.036 / 0.0324</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="K59" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.009</t>
+          <t>0.004 / 0.0035</t>
         </is>
       </c>
       <c r="L59" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.009</t>
+          <t>0.004 / 0.0035</t>
         </is>
       </c>
       <c r="M59" s="16" t="inlineStr">
         <is>
-          <t>1.1 / 1</t>
+          <t>0.55 / 0.48</t>
         </is>
       </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
-          <t>0.703636 / 0.633273</t>
+          <t>0.161948 / 0.144351</t>
         </is>
       </c>
       <c r="O59" s="16" t="inlineStr">
         <is>
-          <t>Continuous strand / tube annealing.</t>
+          <t>Roughing mill: ~30-40 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>Annealing</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C60" s="16" t="inlineStr">
         <is>
-          <t>Induction Annealing</t>
+          <t>Crop Shearing / Intermediate Heating</t>
         </is>
       </c>
       <c r="D60" s="16" t="inlineStr">
@@ -13725,65 +13225,65 @@
         </is>
       </c>
       <c r="E60" s="16" t="n">
-        <v>714.2859999999999</v>
+        <v>25.974</v>
       </c>
       <c r="F60" s="16" t="n">
-        <v>300</v>
+        <v>7.79221</v>
       </c>
       <c r="G60" s="16" t="n">
-        <v>649.351</v>
+        <v>23.3766</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>280</v>
+        <v>7.01299</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.015 / 0.013</t>
         </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.00525 / 0.00455</t>
         </is>
       </c>
       <c r="K60" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.004 / 0.0035</t>
         </is>
       </c>
       <c r="L60" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.004 / 0.0035</t>
         </is>
       </c>
       <c r="M60" s="16" t="inlineStr">
         <is>
-          <t>0.75 / 0.68</t>
+          <t>0.65 / 0.58</t>
         </is>
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>1.11571 / 1.04014</t>
+          <t>0.121802 / 0.106497</t>
         </is>
       </c>
       <c r="O60" s="16" t="inlineStr">
         <is>
-          <t>Induction heating to solution temperature takes ~250-320 kWh/t.</t>
+          <t>Crop shear and coil box / edge heating: ~5-10 kWh/t and little fuel.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>Descaling</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C61" s="16" t="inlineStr">
         <is>
-          <t>Hydraulic High Pressure Spraying</t>
+          <t>Finishing Rolling Train</t>
         </is>
       </c>
       <c r="D61" s="16" t="inlineStr">
@@ -13792,65 +13292,65 @@
         </is>
       </c>
       <c r="E61" s="16" t="n">
-        <v>28.5714</v>
+        <v>181.818</v>
       </c>
       <c r="F61" s="16" t="n">
-        <v>10</v>
+        <v>50.9091</v>
       </c>
       <c r="G61" s="16" t="n">
-        <v>25.974</v>
+        <v>162.338</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>9.090909999999999</v>
+        <v>45.4545</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.001</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="K61" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.006 / 0.005</t>
         </is>
       </c>
       <c r="L61" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.006 / 0.005</t>
         </is>
       </c>
       <c r="M61" s="16" t="inlineStr">
         <is>
-          <t>0.2 / 0.18</t>
+          <t>0.85 / 0.75</t>
         </is>
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>0.0538571 / 0.0505844</t>
+          <t>0.218987 / 0.195779</t>
         </is>
       </c>
       <c r="O61" s="16" t="inlineStr">
         <is>
-          <t>HP spray descaling: ~8-12 kWh/t.</t>
+          <t>Finishing train: ~45-60 kWh/t for stainless strip.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>Descaling</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C62" s="16" t="inlineStr">
         <is>
-          <t>Mechanical Impingement Shot Blasting</t>
+          <t>Controlled Cooling</t>
         </is>
       </c>
       <c r="D62" s="16" t="inlineStr">
@@ -13859,65 +13359,65 @@
         </is>
       </c>
       <c r="E62" s="16" t="n">
-        <v>58.4416</v>
+        <v>32.4675</v>
       </c>
       <c r="F62" s="16" t="n">
-        <v>26.2987</v>
+        <v>6.49351</v>
       </c>
       <c r="G62" s="16" t="n">
-        <v>51.9481</v>
+        <v>28.5714</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>23.3766</v>
+        <v>5.71429</v>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
+          <t>0.0005 / 0.0004</t>
+        </is>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>0.0005 / 0.0004</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
           <t>0.001 / 0.0009</t>
         </is>
       </c>
-      <c r="J62" s="16" t="inlineStr">
+      <c r="L62" s="16" t="inlineStr">
         <is>
           <t>0.001 / 0.0009</t>
         </is>
       </c>
-      <c r="K62" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.013</t>
-        </is>
-      </c>
-      <c r="L62" s="16" t="inlineStr">
-        <is>
-          <t>0.015 / 0.013</t>
-        </is>
-      </c>
       <c r="M62" s="16" t="inlineStr">
         <is>
-          <t>0.42 / 0.38</t>
+          <t>0.2 / 0.18</t>
         </is>
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>0.112532 / 0.100227</t>
+          <t>0.0323052 / 0.0277143</t>
         </is>
       </c>
       <c r="O62" s="16" t="inlineStr">
         <is>
-          <t>Shot blasting: ~20-30 kWh/t.</t>
+          <t>Laminar cooling pumps: ~5-8 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>Descaling</t>
+          <t>Hot Rolling</t>
         </is>
       </c>
       <c r="C63" s="16" t="inlineStr">
         <is>
-          <t>Flex and Stretch Mechanical Scale Breakers</t>
+          <t>Coiling or Plate Shearing</t>
         </is>
       </c>
       <c r="D63" s="16" t="inlineStr">
@@ -13926,65 +13426,65 @@
         </is>
       </c>
       <c r="E63" s="16" t="n">
-        <v>32.4675</v>
+        <v>38.961</v>
       </c>
       <c r="F63" s="16" t="n">
-        <v>11.3636</v>
+        <v>7.01299</v>
       </c>
       <c r="G63" s="16" t="n">
-        <v>28.5714</v>
+        <v>35.0649</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>10</v>
+        <v>6.31169</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="K63" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0027</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="L63" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0027</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="M63" s="16" t="inlineStr">
         <is>
-          <t>0.22 / 0.2</t>
+          <t>0.15 / 0.13</t>
         </is>
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>0.0498377 / 0.0431429</t>
+          <t>0.0431039 / 0.0387935</t>
         </is>
       </c>
       <c r="O63" s="16" t="inlineStr">
         <is>
-          <t>Scale breaker: ~8-12 kWh/t.</t>
+          <t>Down-coiler or plate shear: ~5-8 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>Descaling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C64" s="16" t="inlineStr">
         <is>
-          <t>Molten Salt Conditioning</t>
+          <t>Solution Annealing</t>
         </is>
       </c>
       <c r="D64" s="16" t="inlineStr">
@@ -13996,62 +13496,62 @@
         <v>38.961</v>
       </c>
       <c r="F64" s="16" t="n">
-        <v>17.5325</v>
+        <v>25.3247</v>
       </c>
       <c r="G64" s="16" t="n">
-        <v>35.0649</v>
+        <v>36.3636</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>15.7792</v>
+        <v>23.6364</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
-          <t>0.025 / 0.023</t>
+          <t>0.06 / 0.055</t>
         </is>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.0184</t>
+          <t>0.054 / 0.0495</t>
         </is>
       </c>
       <c r="K64" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.015 / 0.014</t>
         </is>
       </c>
       <c r="L64" s="16" t="inlineStr">
         <is>
-          <t>0.03 / 0.027</t>
+          <t>0.015 / 0.014</t>
         </is>
       </c>
       <c r="M64" s="16" t="inlineStr">
         <is>
-          <t>1.1 / 1</t>
+          <t>1.6 / 1.45</t>
         </is>
       </c>
       <c r="N64" s="16" t="inlineStr">
         <is>
-          <t>0.42026 / 0.385377</t>
+          <t>1.05545 / 0.969019</t>
         </is>
       </c>
       <c r="O64" s="16" t="inlineStr">
         <is>
-          <t>Salt bath: gas-heated, electricity ~15-20 kWh/t.</t>
+          <t>Gas-fired solution annealing: ~0.8-1.1 GJ/t fuel, ~20-30 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="n">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>Descaling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C65" s="16" t="inlineStr">
         <is>
-          <t>Ultrasonic Bath Agitation</t>
+          <t>Subcritical Annealing</t>
         </is>
       </c>
       <c r="D65" s="16" t="inlineStr">
@@ -14060,65 +13560,65 @@
         </is>
       </c>
       <c r="E65" s="16" t="n">
-        <v>36.3636</v>
+        <v>23.3766</v>
       </c>
       <c r="F65" s="16" t="n">
-        <v>12.7273</v>
+        <v>15.1948</v>
       </c>
       <c r="G65" s="16" t="n">
-        <v>32.4675</v>
+        <v>20.7792</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>11.3636</v>
+        <v>13.5065</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
-          <t>0.0003 / 0.00025</t>
+          <t>0.035 / 0.032</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>0.0003 / 0.00025</t>
+          <t>0.0315 / 0.0288</t>
         </is>
       </c>
       <c r="K65" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.009 / 0.008</t>
         </is>
       </c>
       <c r="L65" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.009 / 0.008</t>
         </is>
       </c>
       <c r="M65" s="16" t="inlineStr">
         <is>
-          <t>0.25 / 0.22</t>
+          <t>0.95 / 0.85</t>
         </is>
       </c>
       <c r="N65" s="16" t="inlineStr">
         <is>
-          <t>0.0511753 / 0.0453734</t>
+          <t>0.617201 / 0.562909</t>
         </is>
       </c>
       <c r="O65" s="16" t="inlineStr">
         <is>
-          <t>Ultrasonic agitation: ~10-15 kWh/t.</t>
+          <t>Subcritical anneal: lower soak temperature.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>Pickling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C66" s="16" t="inlineStr">
         <is>
-          <t>Continuous Tank Pickling</t>
+          <t>Full Annealing / Tempering</t>
         </is>
       </c>
       <c r="D66" s="16" t="inlineStr">
@@ -14127,65 +13627,65 @@
         </is>
       </c>
       <c r="E66" s="16" t="n">
-        <v>38.961</v>
+        <v>32.4675</v>
       </c>
       <c r="F66" s="16" t="n">
-        <v>25.3247</v>
+        <v>21.1039</v>
       </c>
       <c r="G66" s="16" t="n">
-        <v>35.0649</v>
+        <v>28.5714</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>22.7922</v>
+        <v>18.5714</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
-          <t>0.008 / 0.007</t>
+          <t>0.05 / 0.045</t>
         </is>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>0.008 / 0.007</t>
+          <t>0.045 / 0.0405</t>
         </is>
       </c>
       <c r="K66" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.045</t>
+          <t>0.012 / 0.011</t>
         </is>
       </c>
       <c r="L66" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.045</t>
+          <t>0.012 / 0.011</t>
         </is>
       </c>
       <c r="M66" s="16" t="inlineStr">
         <is>
-          <t>0.55 / 0.5</t>
+          <t>1.35 / 1.2</t>
         </is>
       </c>
       <c r="N66" s="16" t="inlineStr">
         <is>
-          <t>0.234026 / 0.207052</t>
+          <t>0.879545 / 0.790071</t>
         </is>
       </c>
       <c r="O66" s="16" t="inlineStr">
         <is>
-          <t>Tank pickling pumps, heating and acid regeneration auxiliaries: ~20-30 kWh/t.</t>
+          <t>Full anneal / temper: batch furnace.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Pickling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C67" s="16" t="inlineStr">
         <is>
-          <t>Batch Acid Bath</t>
+          <t>Bright Annealing</t>
         </is>
       </c>
       <c r="D67" s="16" t="inlineStr">
@@ -14194,65 +13694,65 @@
         </is>
       </c>
       <c r="E67" s="16" t="n">
-        <v>25.974</v>
+        <v>58.4416</v>
       </c>
       <c r="F67" s="16" t="n">
-        <v>16.8831</v>
+        <v>46.7532</v>
       </c>
       <c r="G67" s="16" t="n">
-        <v>23.3766</v>
+        <v>51.9481</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>15.1948</v>
+        <v>41.5584</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.009</t>
+          <t>0.055 / 0.05</t>
         </is>
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>0.01 / 0.009</t>
+          <t>0.044 / 0.04</t>
         </is>
       </c>
       <c r="K67" s="16" t="inlineStr">
         <is>
-          <t>0.055 / 0.05</t>
+          <t>0.025 / 0.022</t>
         </is>
       </c>
       <c r="L67" s="16" t="inlineStr">
         <is>
-          <t>0.055 / 0.05</t>
+          <t>0.025 / 0.022</t>
         </is>
       </c>
       <c r="M67" s="16" t="inlineStr">
         <is>
-          <t>0.65 / 0.58</t>
+          <t>1.9 / 1.7</t>
         </is>
       </c>
       <c r="N67" s="16" t="inlineStr">
         <is>
-          <t>0.239351 / 0.215416</t>
+          <t>0.954026 / 0.863896</t>
         </is>
       </c>
       <c r="O67" s="16" t="inlineStr">
         <is>
-          <t>Batch pickling.</t>
+          <t>Bright annealing in hydrogen / cracked ammonia.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Pickling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C68" s="16" t="inlineStr">
         <is>
-          <t>Pickle Paste / Gel</t>
+          <t>Open Annealing / Pickling</t>
         </is>
       </c>
       <c r="D68" s="16" t="inlineStr">
@@ -14261,65 +13761,65 @@
         </is>
       </c>
       <c r="E68" s="16" t="n">
-        <v>6.49351</v>
+        <v>45.4545</v>
       </c>
       <c r="F68" s="16" t="n">
-        <v>6.49351</v>
+        <v>29.5455</v>
       </c>
       <c r="G68" s="16" t="n">
-        <v>5.84416</v>
+        <v>41.5584</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>5.84416</v>
+        <v>27.013</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.06 / 0.055</t>
         </is>
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.054 / 0.0495</t>
         </is>
       </c>
       <c r="K68" s="16" t="inlineStr">
         <is>
-          <t>0.035 / 0.032</t>
+          <t>0.04 / 0.036</t>
         </is>
       </c>
       <c r="L68" s="16" t="inlineStr">
         <is>
-          <t>0.035 / 0.032</t>
+          <t>0.04 / 0.036</t>
         </is>
       </c>
       <c r="M68" s="16" t="inlineStr">
         <is>
-          <t>0.08 / 0.07</t>
+          <t>1.7 / 1.55</t>
         </is>
       </c>
       <c r="N68" s="16" t="inlineStr">
         <is>
-          <t>0.08 / 0.07</t>
+          <t>1.07065 / 0.981175</t>
         </is>
       </c>
       <c r="O68" s="16" t="inlineStr">
         <is>
-          <t>Paste pickling: manual, minimal energy; unchanged.</t>
+          <t>Open annealing with pickling.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="16" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>Pickling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C69" s="16" t="inlineStr">
         <is>
-          <t>Spray Pickling</t>
+          <t>Continuous Strand / Tube Annealing</t>
         </is>
       </c>
       <c r="D69" s="16" t="inlineStr">
@@ -14328,65 +13828,65 @@
         </is>
       </c>
       <c r="E69" s="16" t="n">
-        <v>45.4545</v>
+        <v>25.974</v>
       </c>
       <c r="F69" s="16" t="n">
-        <v>29.5455</v>
+        <v>16.8831</v>
       </c>
       <c r="G69" s="16" t="n">
-        <v>41.5584</v>
+        <v>23.3766</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>27.013</v>
+        <v>15.1948</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.0054</t>
+          <t>0.04 / 0.036</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>0.006 / 0.0054</t>
+          <t>0.036 / 0.0324</t>
         </is>
       </c>
       <c r="K69" s="16" t="inlineStr">
         <is>
-          <t>0.038 / 0.034</t>
+          <t>0.01 / 0.009</t>
         </is>
       </c>
       <c r="L69" s="16" t="inlineStr">
         <is>
-          <t>0.038 / 0.034</t>
+          <t>0.01 / 0.009</t>
         </is>
       </c>
       <c r="M69" s="16" t="inlineStr">
         <is>
-          <t>0.48 / 0.43</t>
+          <t>1.1 / 1</t>
         </is>
       </c>
       <c r="N69" s="16" t="inlineStr">
         <is>
-          <t>0.213506 / 0.193675</t>
+          <t>0.703636 / 0.633273</t>
         </is>
       </c>
       <c r="O69" s="16" t="inlineStr">
         <is>
-          <t>Spray pickling.</t>
+          <t>Continuous strand / tube annealing.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="16" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Annealing</t>
         </is>
       </c>
       <c r="C70" s="16" t="inlineStr">
         <is>
-          <t>20-High Cluster Mill (Z-Mill / Sendzimir)</t>
+          <t>Induction Annealing</t>
         </is>
       </c>
       <c r="D70" s="16" t="inlineStr">
@@ -14395,65 +13895,65 @@
         </is>
       </c>
       <c r="E70" s="16" t="n">
-        <v>207.792</v>
+        <v>714.2859999999999</v>
       </c>
       <c r="F70" s="16" t="n">
-        <v>145.455</v>
+        <v>300</v>
       </c>
       <c r="G70" s="16" t="n">
-        <v>188.312</v>
+        <v>649.351</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>131.818</v>
+        <v>280</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="K70" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.018</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="L70" s="16" t="inlineStr">
         <is>
-          <t>0.02 / 0.018</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="M70" s="16" t="inlineStr">
         <is>
-          <t>0.65 / 0.58</t>
+          <t>0.75 / 0.68</t>
         </is>
       </c>
       <c r="N70" s="16" t="inlineStr">
         <is>
-          <t>0.541494 / 0.490617</t>
+          <t>1.11571 / 1.04014</t>
         </is>
       </c>
       <c r="O70" s="16" t="inlineStr">
         <is>
-          <t>20-Hi Sendzimir: ~120-160 kWh/t depending on total reduction.</t>
+          <t>Induction heating to solution temperature takes ~250-320 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="16" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Descaling</t>
         </is>
       </c>
       <c r="C71" s="16" t="inlineStr">
         <is>
-          <t>18-High Sendzimir Cluster Mill</t>
+          <t>Hydraulic High Pressure Spraying</t>
         </is>
       </c>
       <c r="D71" s="16" t="inlineStr">
@@ -14462,65 +13962,65 @@
         </is>
       </c>
       <c r="E71" s="16" t="n">
-        <v>194.805</v>
+        <v>28.5714</v>
       </c>
       <c r="F71" s="16" t="n">
-        <v>136.364</v>
+        <v>10</v>
       </c>
       <c r="G71" s="16" t="n">
-        <v>175.325</v>
+        <v>25.974</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>122.727</v>
+        <v>9.090909999999999</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.001 / 0.001</t>
         </is>
       </c>
       <c r="K71" s="16" t="inlineStr">
         <is>
-          <t>0.018 / 0.016</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="L71" s="16" t="inlineStr">
         <is>
-          <t>0.018 / 0.016</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="M71" s="16" t="inlineStr">
         <is>
-          <t>0.6 / 0.54</t>
+          <t>0.2 / 0.18</t>
         </is>
       </c>
       <c r="N71" s="16" t="inlineStr">
         <is>
-          <t>0.508766 / 0.45789</t>
+          <t>0.0538571 / 0.0505844</t>
         </is>
       </c>
       <c r="O71" s="16" t="inlineStr">
         <is>
-          <t>18-Hi cluster mill.</t>
+          <t>HP spray descaling: ~8-12 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="16" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Descaling</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
         <is>
-          <t>6-High Universal Crown-Control Mill (UC Mill)</t>
+          <t>Mechanical Impingement Shot Blasting</t>
         </is>
       </c>
       <c r="D72" s="16" t="inlineStr">
@@ -14529,65 +14029,65 @@
         </is>
       </c>
       <c r="E72" s="16" t="n">
-        <v>142.857</v>
+        <v>58.4416</v>
       </c>
       <c r="F72" s="16" t="n">
-        <v>100</v>
+        <v>26.2987</v>
       </c>
       <c r="G72" s="16" t="n">
-        <v>129.87</v>
+        <v>51.9481</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>90.9091</v>
+        <v>23.3766</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
-          <t>0.0008 / 0.0007</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>0.0008 / 0.0007</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="K72" s="16" t="inlineStr">
         <is>
-          <t>0.012 / 0.011</t>
+          <t>0.015 / 0.013</t>
         </is>
       </c>
       <c r="L72" s="16" t="inlineStr">
         <is>
-          <t>0.012 / 0.011</t>
+          <t>0.015 / 0.013</t>
         </is>
       </c>
       <c r="M72" s="16" t="inlineStr">
         <is>
-          <t>0.48 / 0.43</t>
+          <t>0.42 / 0.38</t>
         </is>
       </c>
       <c r="N72" s="16" t="inlineStr">
         <is>
-          <t>0.374286 / 0.339773</t>
+          <t>0.112532 / 0.100227</t>
         </is>
       </c>
       <c r="O72" s="16" t="inlineStr">
         <is>
-          <t>6-Hi UC mill.</t>
+          <t>Shot blasting: ~20-30 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Descaling</t>
         </is>
       </c>
       <c r="C73" s="16" t="inlineStr">
         <is>
-          <t>Continuous Tandem Cold Mill (TCM)</t>
+          <t>Flex and Stretch Mechanical Scale Breakers</t>
         </is>
       </c>
       <c r="D73" s="16" t="inlineStr">
@@ -14596,65 +14096,65 @@
         </is>
       </c>
       <c r="E73" s="16" t="n">
-        <v>168.831</v>
+        <v>32.4675</v>
       </c>
       <c r="F73" s="16" t="n">
-        <v>118.182</v>
+        <v>11.3636</v>
       </c>
       <c r="G73" s="16" t="n">
-        <v>151.948</v>
+        <v>28.5714</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>106.364</v>
+        <v>10</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
-          <t>0.0007 / 0.0006</t>
+          <t>0.0005 / 0.0004</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>0.0007 / 0.0006</t>
+          <t>0.0005 / 0.0004</t>
         </is>
       </c>
       <c r="K73" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.0135</t>
+          <t>0.003 / 0.0027</t>
         </is>
       </c>
       <c r="L73" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.0135</t>
+          <t>0.003 / 0.0027</t>
         </is>
       </c>
       <c r="M73" s="16" t="inlineStr">
         <is>
-          <t>0.55 / 0.49</t>
+          <t>0.22 / 0.2</t>
         </is>
       </c>
       <c r="N73" s="16" t="inlineStr">
         <is>
-          <t>0.437955 / 0.393623</t>
+          <t>0.0498377 / 0.0431429</t>
         </is>
       </c>
       <c r="O73" s="16" t="inlineStr">
         <is>
-          <t>Tandem cold mill.</t>
+          <t>Scale breaker: ~8-12 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Descaling</t>
         </is>
       </c>
       <c r="C74" s="16" t="inlineStr">
         <is>
-          <t>CAPL / AP Line (Continuous Anneal &amp; Pickle Line)</t>
+          <t>Molten Salt Conditioning</t>
         </is>
       </c>
       <c r="D74" s="16" t="inlineStr">
@@ -14663,65 +14163,65 @@
         </is>
       </c>
       <c r="E74" s="16" t="n">
-        <v>42.8571</v>
+        <v>38.961</v>
       </c>
       <c r="F74" s="16" t="n">
-        <v>42.8571</v>
+        <v>17.5325</v>
       </c>
       <c r="G74" s="16" t="n">
-        <v>38.961</v>
+        <v>35.0649</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>38.961</v>
+        <v>15.7792</v>
       </c>
       <c r="I74" s="16" t="inlineStr">
         <is>
-          <t>0.058 / 0.053</t>
+          <t>0.025 / 0.023</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>0.0522 / 0.0477</t>
+          <t>0.02 / 0.0184</t>
         </is>
       </c>
       <c r="K74" s="16" t="inlineStr">
         <is>
-          <t>0.038 / 0.034</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="L74" s="16" t="inlineStr">
         <is>
-          <t>0.038 / 0.034</t>
+          <t>0.03 / 0.027</t>
         </is>
       </c>
       <c r="M74" s="16" t="inlineStr">
         <is>
-          <t>1.65 / 1.5</t>
+          <t>1.1 / 1</t>
         </is>
       </c>
       <c r="N74" s="16" t="inlineStr">
         <is>
-          <t>1.08643 / 0.992045</t>
+          <t>0.42026 / 0.385377</t>
         </is>
       </c>
       <c r="O74" s="16" t="inlineStr">
         <is>
-          <t>CAPL: gas-fired anneal ~0.9-1.0 GJ/t plus pickling; electricity kept.</t>
+          <t>Salt bath: gas-heated, electricity ~15-20 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="16" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Descaling</t>
         </is>
       </c>
       <c r="C75" s="16" t="inlineStr">
         <is>
-          <t>Temper Mill (Skin-Pass)</t>
+          <t>Ultrasonic Bath Agitation</t>
         </is>
       </c>
       <c r="D75" s="16" t="inlineStr">
@@ -14730,16 +14230,16 @@
         </is>
       </c>
       <c r="E75" s="16" t="n">
+        <v>36.3636</v>
+      </c>
+      <c r="F75" s="16" t="n">
+        <v>12.7273</v>
+      </c>
+      <c r="G75" s="16" t="n">
         <v>32.4675</v>
       </c>
-      <c r="F75" s="16" t="n">
-        <v>14.6104</v>
-      </c>
-      <c r="G75" s="16" t="n">
-        <v>28.5714</v>
-      </c>
       <c r="H75" s="16" t="n">
-        <v>12.8571</v>
+        <v>11.3636</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -14753,42 +14253,42 @@
       </c>
       <c r="K75" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0027</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="L75" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0027</t>
+          <t>0.002 / 0.0018</t>
         </is>
       </c>
       <c r="M75" s="16" t="inlineStr">
         <is>
-          <t>0.12 / 0.1</t>
+          <t>0.25 / 0.22</t>
         </is>
       </c>
       <c r="N75" s="16" t="inlineStr">
         <is>
-          <t>0.0579545 / 0.05075</t>
+          <t>0.0511753 / 0.0453734</t>
         </is>
       </c>
       <c r="O75" s="16" t="inlineStr">
         <is>
-          <t>Skin-pass mill: ~10-15 kWh/t.</t>
+          <t>Ultrasonic agitation: ~10-15 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="16" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Pickling</t>
         </is>
       </c>
       <c r="C76" s="16" t="inlineStr">
         <is>
-          <t>Bright Annealing (in-process, Cold Rolling sequence)</t>
+          <t>Continuous Tank Pickling</t>
         </is>
       </c>
       <c r="D76" s="16" t="inlineStr">
@@ -14797,65 +14297,65 @@
         </is>
       </c>
       <c r="E76" s="16" t="n">
-        <v>58.4416</v>
+        <v>38.961</v>
       </c>
       <c r="F76" s="16" t="n">
-        <v>46.7532</v>
+        <v>25.3247</v>
       </c>
       <c r="G76" s="16" t="n">
-        <v>51.9481</v>
+        <v>35.0649</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>41.5584</v>
+        <v>22.7922</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
-          <t>0.055 / 0.05</t>
+          <t>0.008 / 0.007</t>
         </is>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>0.044 / 0.04</t>
+          <t>0.008 / 0.007</t>
         </is>
       </c>
       <c r="K76" s="16" t="inlineStr">
         <is>
-          <t>0.025 / 0.022</t>
+          <t>0.05 / 0.045</t>
         </is>
       </c>
       <c r="L76" s="16" t="inlineStr">
         <is>
-          <t>0.025 / 0.022</t>
+          <t>0.05 / 0.045</t>
         </is>
       </c>
       <c r="M76" s="16" t="inlineStr">
         <is>
-          <t>1.9 / 1.7</t>
+          <t>0.55 / 0.5</t>
         </is>
       </c>
       <c r="N76" s="16" t="inlineStr">
         <is>
-          <t>0.954026 / 0.863896</t>
+          <t>0.234026 / 0.207052</t>
         </is>
       </c>
       <c r="O76" s="16" t="inlineStr">
         <is>
-          <t>Bright annealing in the cold-rolling sequence.</t>
+          <t>Tank pickling pumps, heating and acid regeneration auxiliaries: ~20-30 kWh/t.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="16" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Cold Rolling</t>
+          <t>Pickling</t>
         </is>
       </c>
       <c r="C77" s="16" t="inlineStr">
         <is>
-          <t>Tension Leveling / Slitting Lines</t>
+          <t>Batch Acid Bath</t>
         </is>
       </c>
       <c r="D77" s="16" t="inlineStr">
@@ -14864,65 +14364,65 @@
         </is>
       </c>
       <c r="E77" s="16" t="n">
-        <v>38.961</v>
+        <v>25.974</v>
       </c>
       <c r="F77" s="16" t="n">
-        <v>15.5844</v>
+        <v>16.8831</v>
       </c>
       <c r="G77" s="16" t="n">
-        <v>35.0649</v>
+        <v>23.3766</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>14.026</v>
+        <v>15.1948</v>
       </c>
       <c r="I77" s="16" t="inlineStr">
         <is>
-          <t>0.0004 / 0.00035</t>
+          <t>0.01 / 0.009</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>0.0004 / 0.00035</t>
+          <t>0.01 / 0.009</t>
         </is>
       </c>
       <c r="K77" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0036</t>
+          <t>0.055 / 0.05</t>
         </is>
       </c>
       <c r="L77" s="16" t="inlineStr">
         <is>
-          <t>0.004 / 0.0036</t>
+          <t>0.055 / 0.05</t>
         </is>
       </c>
       <c r="M77" s="16" t="inlineStr">
         <is>
-          <t>0.16 / 0.14</t>
+          <t>0.65 / 0.58</t>
         </is>
       </c>
       <c r="N77" s="16" t="inlineStr">
         <is>
-          <t>0.0632468 / 0.0567435</t>
+          <t>0.239351 / 0.215416</t>
         </is>
       </c>
       <c r="O77" s="16" t="inlineStr">
         <is>
-          <t>Tension levelling and slitting: ~10-15 kWh/t.</t>
+          <t>Batch pickling.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Pickling</t>
         </is>
       </c>
       <c r="C78" s="16" t="inlineStr">
         <is>
-          <t>Packing / Preservation</t>
+          <t>Pickle Paste / Gel</t>
         </is>
       </c>
       <c r="D78" s="16" t="inlineStr">
@@ -14931,65 +14431,65 @@
         </is>
       </c>
       <c r="E78" s="16" t="n">
-        <v>10.3896</v>
+        <v>6.49351</v>
       </c>
       <c r="F78" s="16" t="n">
-        <v>6.23377</v>
+        <v>6.49351</v>
       </c>
       <c r="G78" s="16" t="n">
-        <v>9.090909999999999</v>
+        <v>5.84416</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>5.45455</v>
+        <v>5.84416</v>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0025</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>0.003 / 0.0025</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="K78" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.013</t>
+          <t>0.035 / 0.032</t>
         </is>
       </c>
       <c r="L78" s="16" t="inlineStr">
         <is>
-          <t>0.015 / 0.013</t>
+          <t>0.035 / 0.032</t>
         </is>
       </c>
       <c r="M78" s="16" t="inlineStr">
         <is>
-          <t>0.06 / 0.05</t>
+          <t>0.08 / 0.07</t>
         </is>
       </c>
       <c r="N78" s="16" t="inlineStr">
         <is>
-          <t>0.0629821 / 0.0534201</t>
+          <t>0.08 / 0.07</t>
         </is>
       </c>
       <c r="O78" s="16" t="inlineStr">
         <is>
-          <t>Packing: strapping and wrapping machines, ~5-8 kWh/t.</t>
+          <t>Paste pickling: manual, minimal energy; unchanged.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="16" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Pickling</t>
         </is>
       </c>
       <c r="C79" s="16" t="inlineStr">
         <is>
-          <t>Warehousing</t>
+          <t>Spray Pickling</t>
         </is>
       </c>
       <c r="D79" s="16" t="inlineStr">
@@ -14998,65 +14498,65 @@
         </is>
       </c>
       <c r="E79" s="16" t="n">
-        <v>19.4805</v>
+        <v>45.4545</v>
       </c>
       <c r="F79" s="16" t="n">
-        <v>4.87013</v>
+        <v>29.5455</v>
       </c>
       <c r="G79" s="16" t="n">
-        <v>16.8831</v>
+        <v>41.5584</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>4.22078</v>
+        <v>27.013</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.006 / 0.0054</t>
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>0.002 / 0.0018</t>
+          <t>0.006 / 0.0054</t>
         </is>
       </c>
       <c r="K79" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.038 / 0.034</t>
         </is>
       </c>
       <c r="L79" s="16" t="inlineStr">
         <is>
-          <t>0.001 / 0.0009</t>
+          <t>0.038 / 0.034</t>
         </is>
       </c>
       <c r="M79" s="16" t="inlineStr">
         <is>
-          <t>0.12 / 0.1</t>
+          <t>0.48 / 0.43</t>
         </is>
       </c>
       <c r="N79" s="16" t="inlineStr">
         <is>
-          <t>0.0445595 / 0.0395191</t>
+          <t>0.213506 / 0.193675</t>
         </is>
       </c>
       <c r="O79" s="16" t="inlineStr">
         <is>
-          <t>Warehousing: lighting and cranes, ~4-6 kWh/t.</t>
+          <t>Spray pickling.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Outbound</t>
+          <t>Cold Rolling</t>
         </is>
       </c>
       <c r="C80" s="16" t="inlineStr">
         <is>
-          <t>Picking</t>
+          <t>20-High Cluster Mill (Z-Mill / Sendzimir)</t>
         </is>
       </c>
       <c r="D80" s="16" t="inlineStr">
@@ -15065,83 +14565,753 @@
         </is>
       </c>
       <c r="E80" s="16" t="n">
-        <v>7.79221</v>
+        <v>207.792</v>
       </c>
       <c r="F80" s="16" t="n">
-        <v>3.11688</v>
+        <v>145.455</v>
       </c>
       <c r="G80" s="16" t="n">
-        <v>6.88312</v>
+        <v>188.312</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>2.75325</v>
+        <v>131.818</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
-          <t>0.0015 / 0.0013</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>0.0015 / 0.0013</t>
+          <t>0.001 / 0.0009</t>
         </is>
       </c>
       <c r="K80" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.02 / 0.018</t>
         </is>
       </c>
       <c r="L80" s="16" t="inlineStr">
         <is>
-          <t>0.0005 / 0.0004</t>
+          <t>0.02 / 0.018</t>
         </is>
       </c>
       <c r="M80" s="16" t="inlineStr">
         <is>
-          <t>0.05 / 0.045</t>
+          <t>0.65 / 0.58</t>
         </is>
       </c>
       <c r="N80" s="16" t="inlineStr">
         <is>
-          <t>0.031491 / 0.0274793</t>
+          <t>0.541494 / 0.490617</t>
         </is>
       </c>
       <c r="O80" s="16" t="inlineStr">
         <is>
-          <t>Picking: forklifts and cranes, ~2-4 kWh/t.</t>
+          <t>20-Hi Sendzimir: ~120-160 kWh/t depending on total reduction.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="n">
+        <v>57</v>
+      </c>
+      <c r="B81" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>18-High Sendzimir Cluster Mill</t>
+        </is>
+      </c>
+      <c r="D81" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E81" s="16" t="n">
+        <v>194.805</v>
+      </c>
+      <c r="F81" s="16" t="n">
+        <v>136.364</v>
+      </c>
+      <c r="G81" s="16" t="n">
+        <v>175.325</v>
+      </c>
+      <c r="H81" s="16" t="n">
+        <v>122.727</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>0.001 / 0.0009</t>
+        </is>
+      </c>
+      <c r="J81" s="16" t="inlineStr">
+        <is>
+          <t>0.001 / 0.0009</t>
+        </is>
+      </c>
+      <c r="K81" s="16" t="inlineStr">
+        <is>
+          <t>0.018 / 0.016</t>
+        </is>
+      </c>
+      <c r="L81" s="16" t="inlineStr">
+        <is>
+          <t>0.018 / 0.016</t>
+        </is>
+      </c>
+      <c r="M81" s="16" t="inlineStr">
+        <is>
+          <t>0.6 / 0.54</t>
+        </is>
+      </c>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>0.508766 / 0.45789</t>
+        </is>
+      </c>
+      <c r="O81" s="16" t="inlineStr">
+        <is>
+          <t>18-Hi cluster mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="16" t="n">
+        <v>58</v>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C82" s="16" t="inlineStr">
+        <is>
+          <t>6-High Universal Crown-Control Mill (UC Mill)</t>
+        </is>
+      </c>
+      <c r="D82" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E82" s="16" t="n">
+        <v>142.857</v>
+      </c>
+      <c r="F82" s="16" t="n">
+        <v>100</v>
+      </c>
+      <c r="G82" s="16" t="n">
+        <v>129.87</v>
+      </c>
+      <c r="H82" s="16" t="n">
+        <v>90.9091</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>0.0008 / 0.0007</t>
+        </is>
+      </c>
+      <c r="J82" s="16" t="inlineStr">
+        <is>
+          <t>0.0008 / 0.0007</t>
+        </is>
+      </c>
+      <c r="K82" s="16" t="inlineStr">
+        <is>
+          <t>0.012 / 0.011</t>
+        </is>
+      </c>
+      <c r="L82" s="16" t="inlineStr">
+        <is>
+          <t>0.012 / 0.011</t>
+        </is>
+      </c>
+      <c r="M82" s="16" t="inlineStr">
+        <is>
+          <t>0.48 / 0.43</t>
+        </is>
+      </c>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>0.374286 / 0.339773</t>
+        </is>
+      </c>
+      <c r="O82" s="16" t="inlineStr">
+        <is>
+          <t>6-Hi UC mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="16" t="n">
+        <v>59</v>
+      </c>
+      <c r="B83" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C83" s="16" t="inlineStr">
+        <is>
+          <t>Continuous Tandem Cold Mill (TCM)</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E83" s="16" t="n">
+        <v>168.831</v>
+      </c>
+      <c r="F83" s="16" t="n">
+        <v>118.182</v>
+      </c>
+      <c r="G83" s="16" t="n">
+        <v>151.948</v>
+      </c>
+      <c r="H83" s="16" t="n">
+        <v>106.364</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>0.0007 / 0.0006</t>
+        </is>
+      </c>
+      <c r="J83" s="16" t="inlineStr">
+        <is>
+          <t>0.0007 / 0.0006</t>
+        </is>
+      </c>
+      <c r="K83" s="16" t="inlineStr">
+        <is>
+          <t>0.015 / 0.0135</t>
+        </is>
+      </c>
+      <c r="L83" s="16" t="inlineStr">
+        <is>
+          <t>0.015 / 0.0135</t>
+        </is>
+      </c>
+      <c r="M83" s="16" t="inlineStr">
+        <is>
+          <t>0.55 / 0.49</t>
+        </is>
+      </c>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>0.437955 / 0.393623</t>
+        </is>
+      </c>
+      <c r="O83" s="16" t="inlineStr">
+        <is>
+          <t>Tandem cold mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="16" t="n">
+        <v>60</v>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C84" s="16" t="inlineStr">
+        <is>
+          <t>CAPL / AP Line (Continuous Anneal &amp; Pickle Line)</t>
+        </is>
+      </c>
+      <c r="D84" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E84" s="16" t="n">
+        <v>42.8571</v>
+      </c>
+      <c r="F84" s="16" t="n">
+        <v>42.8571</v>
+      </c>
+      <c r="G84" s="16" t="n">
+        <v>38.961</v>
+      </c>
+      <c r="H84" s="16" t="n">
+        <v>38.961</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>0.058 / 0.053</t>
+        </is>
+      </c>
+      <c r="J84" s="16" t="inlineStr">
+        <is>
+          <t>0.0522 / 0.0477</t>
+        </is>
+      </c>
+      <c r="K84" s="16" t="inlineStr">
+        <is>
+          <t>0.038 / 0.034</t>
+        </is>
+      </c>
+      <c r="L84" s="16" t="inlineStr">
+        <is>
+          <t>0.038 / 0.034</t>
+        </is>
+      </c>
+      <c r="M84" s="16" t="inlineStr">
+        <is>
+          <t>1.65 / 1.5</t>
+        </is>
+      </c>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>1.08643 / 0.992045</t>
+        </is>
+      </c>
+      <c r="O84" s="16" t="inlineStr">
+        <is>
+          <t>CAPL: gas-fired anneal ~0.9-1.0 GJ/t plus pickling; electricity kept.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="16" t="n">
+        <v>61</v>
+      </c>
+      <c r="B85" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C85" s="16" t="inlineStr">
+        <is>
+          <t>Temper Mill (Skin-Pass)</t>
+        </is>
+      </c>
+      <c r="D85" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E85" s="16" t="n">
+        <v>32.4675</v>
+      </c>
+      <c r="F85" s="16" t="n">
+        <v>14.6104</v>
+      </c>
+      <c r="G85" s="16" t="n">
+        <v>28.5714</v>
+      </c>
+      <c r="H85" s="16" t="n">
+        <v>12.8571</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>0.0003 / 0.00025</t>
+        </is>
+      </c>
+      <c r="J85" s="16" t="inlineStr">
+        <is>
+          <t>0.0003 / 0.00025</t>
+        </is>
+      </c>
+      <c r="K85" s="16" t="inlineStr">
+        <is>
+          <t>0.003 / 0.0027</t>
+        </is>
+      </c>
+      <c r="L85" s="16" t="inlineStr">
+        <is>
+          <t>0.003 / 0.0027</t>
+        </is>
+      </c>
+      <c r="M85" s="16" t="inlineStr">
+        <is>
+          <t>0.12 / 0.1</t>
+        </is>
+      </c>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>0.0579545 / 0.05075</t>
+        </is>
+      </c>
+      <c r="O85" s="16" t="inlineStr">
+        <is>
+          <t>Skin-pass mill: ~10-15 kWh/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="16" t="n">
+        <v>62</v>
+      </c>
+      <c r="B86" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>Bright Annealing (in-process, Cold Rolling sequence)</t>
+        </is>
+      </c>
+      <c r="D86" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E86" s="16" t="n">
+        <v>58.4416</v>
+      </c>
+      <c r="F86" s="16" t="n">
+        <v>46.7532</v>
+      </c>
+      <c r="G86" s="16" t="n">
+        <v>51.9481</v>
+      </c>
+      <c r="H86" s="16" t="n">
+        <v>41.5584</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>0.055 / 0.05</t>
+        </is>
+      </c>
+      <c r="J86" s="16" t="inlineStr">
+        <is>
+          <t>0.044 / 0.04</t>
+        </is>
+      </c>
+      <c r="K86" s="16" t="inlineStr">
+        <is>
+          <t>0.025 / 0.022</t>
+        </is>
+      </c>
+      <c r="L86" s="16" t="inlineStr">
+        <is>
+          <t>0.025 / 0.022</t>
+        </is>
+      </c>
+      <c r="M86" s="16" t="inlineStr">
+        <is>
+          <t>1.9 / 1.7</t>
+        </is>
+      </c>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>0.954026 / 0.863896</t>
+        </is>
+      </c>
+      <c r="O86" s="16" t="inlineStr">
+        <is>
+          <t>Bright annealing in the cold-rolling sequence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="16" t="n">
+        <v>63</v>
+      </c>
+      <c r="B87" s="16" t="inlineStr">
+        <is>
+          <t>Cold Rolling</t>
+        </is>
+      </c>
+      <c r="C87" s="16" t="inlineStr">
+        <is>
+          <t>Tension Leveling / Slitting Lines</t>
+        </is>
+      </c>
+      <c r="D87" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E87" s="16" t="n">
+        <v>38.961</v>
+      </c>
+      <c r="F87" s="16" t="n">
+        <v>15.5844</v>
+      </c>
+      <c r="G87" s="16" t="n">
+        <v>35.0649</v>
+      </c>
+      <c r="H87" s="16" t="n">
+        <v>14.026</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>0.0004 / 0.00035</t>
+        </is>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>0.0004 / 0.00035</t>
+        </is>
+      </c>
+      <c r="K87" s="16" t="inlineStr">
+        <is>
+          <t>0.004 / 0.0036</t>
+        </is>
+      </c>
+      <c r="L87" s="16" t="inlineStr">
+        <is>
+          <t>0.004 / 0.0036</t>
+        </is>
+      </c>
+      <c r="M87" s="16" t="inlineStr">
+        <is>
+          <t>0.16 / 0.14</t>
+        </is>
+      </c>
+      <c r="N87" s="16" t="inlineStr">
+        <is>
+          <t>0.0632468 / 0.0567435</t>
+        </is>
+      </c>
+      <c r="O87" s="16" t="inlineStr">
+        <is>
+          <t>Tension levelling and slitting: ~10-15 kWh/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="16" t="n">
+        <v>64</v>
+      </c>
+      <c r="B88" s="16" t="inlineStr">
+        <is>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="C88" s="16" t="inlineStr">
+        <is>
+          <t>Packing / Preservation</t>
+        </is>
+      </c>
+      <c r="D88" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E88" s="16" t="n">
+        <v>10.3896</v>
+      </c>
+      <c r="F88" s="16" t="n">
+        <v>6.23377</v>
+      </c>
+      <c r="G88" s="16" t="n">
+        <v>9.090909999999999</v>
+      </c>
+      <c r="H88" s="16" t="n">
+        <v>5.45455</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>0.003 / 0.0025</t>
+        </is>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>0.003 / 0.0025</t>
+        </is>
+      </c>
+      <c r="K88" s="16" t="inlineStr">
+        <is>
+          <t>0.015 / 0.013</t>
+        </is>
+      </c>
+      <c r="L88" s="16" t="inlineStr">
+        <is>
+          <t>0.015 / 0.013</t>
+        </is>
+      </c>
+      <c r="M88" s="16" t="inlineStr">
+        <is>
+          <t>0.06 / 0.05</t>
+        </is>
+      </c>
+      <c r="N88" s="16" t="inlineStr">
+        <is>
+          <t>0.0629821 / 0.0534201</t>
+        </is>
+      </c>
+      <c r="O88" s="16" t="inlineStr">
+        <is>
+          <t>Packing: strapping and wrapping machines, ~5-8 kWh/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="16" t="n">
+        <v>65</v>
+      </c>
+      <c r="B89" s="16" t="inlineStr">
+        <is>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="C89" s="16" t="inlineStr">
+        <is>
+          <t>Warehousing</t>
+        </is>
+      </c>
+      <c r="D89" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E89" s="16" t="n">
+        <v>19.4805</v>
+      </c>
+      <c r="F89" s="16" t="n">
+        <v>4.87013</v>
+      </c>
+      <c r="G89" s="16" t="n">
+        <v>16.8831</v>
+      </c>
+      <c r="H89" s="16" t="n">
+        <v>4.22078</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>0.002 / 0.0018</t>
+        </is>
+      </c>
+      <c r="J89" s="16" t="inlineStr">
+        <is>
+          <t>0.002 / 0.0018</t>
+        </is>
+      </c>
+      <c r="K89" s="16" t="inlineStr">
+        <is>
+          <t>0.001 / 0.0009</t>
+        </is>
+      </c>
+      <c r="L89" s="16" t="inlineStr">
+        <is>
+          <t>0.001 / 0.0009</t>
+        </is>
+      </c>
+      <c r="M89" s="16" t="inlineStr">
+        <is>
+          <t>0.12 / 0.1</t>
+        </is>
+      </c>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>0.0445595 / 0.0395191</t>
+        </is>
+      </c>
+      <c r="O89" s="16" t="inlineStr">
+        <is>
+          <t>Warehousing: lighting and cranes, ~4-6 kWh/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>Outbound</t>
+        </is>
+      </c>
+      <c r="C90" s="16" t="inlineStr">
+        <is>
+          <t>Picking</t>
+        </is>
+      </c>
+      <c r="D90" s="16" t="inlineStr">
+        <is>
+          <t>General (all types)</t>
+        </is>
+      </c>
+      <c r="E90" s="16" t="n">
+        <v>7.79221</v>
+      </c>
+      <c r="F90" s="16" t="n">
+        <v>3.11688</v>
+      </c>
+      <c r="G90" s="16" t="n">
+        <v>6.88312</v>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>2.75325</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>0.0015 / 0.0013</t>
+        </is>
+      </c>
+      <c r="J90" s="16" t="inlineStr">
+        <is>
+          <t>0.0015 / 0.0013</t>
+        </is>
+      </c>
+      <c r="K90" s="16" t="inlineStr">
+        <is>
+          <t>0.0005 / 0.0004</t>
+        </is>
+      </c>
+      <c r="L90" s="16" t="inlineStr">
+        <is>
+          <t>0.0005 / 0.0004</t>
+        </is>
+      </c>
+      <c r="M90" s="16" t="inlineStr">
+        <is>
+          <t>0.05 / 0.045</t>
+        </is>
+      </c>
+      <c r="N90" s="16" t="inlineStr">
+        <is>
+          <t>0.031491 / 0.0274793</t>
+        </is>
+      </c>
+      <c r="O90" s="16" t="inlineStr">
+        <is>
+          <t>Picking: forklifts and cranes, ~2-4 kWh/t.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="16" t="n">
         <v>67</v>
       </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>Outbound</t>
         </is>
       </c>
-      <c r="C81" s="16" t="inlineStr">
+      <c r="C91" s="16" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D81" s="16" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>Train + Road Mix (p/q)</t>
         </is>
       </c>
-      <c r="E81" s="16" t="inlineStr"/>
-      <c r="F81" s="16" t="inlineStr"/>
-      <c r="G81" s="16" t="inlineStr"/>
-      <c r="H81" s="16" t="inlineStr"/>
-      <c r="I81" s="16" t="inlineStr"/>
-      <c r="J81" s="16" t="inlineStr"/>
-      <c r="K81" s="16" t="inlineStr"/>
-      <c r="L81" s="16" t="inlineStr"/>
-      <c r="M81" s="16" t="inlineStr"/>
-      <c r="N81" s="16" t="inlineStr"/>
-      <c r="O81" s="16" t="inlineStr">
+      <c r="E91" s="16" t="inlineStr"/>
+      <c r="F91" s="16" t="inlineStr"/>
+      <c r="G91" s="16" t="inlineStr"/>
+      <c r="H91" s="16" t="inlineStr"/>
+      <c r="I91" s="16" t="inlineStr"/>
+      <c r="J91" s="16" t="inlineStr"/>
+      <c r="K91" s="16" t="inlineStr"/>
+      <c r="L91" s="16" t="inlineStr"/>
+      <c r="M91" s="16" t="inlineStr"/>
+      <c r="N91" s="16" t="inlineStr"/>
+      <c r="O91" s="16" t="inlineStr">
         <is>
           <t>Transport row: unchanged.</t>
         </is>

--- a/data/source/Stainless_Steel_Carbon_Accounting_Grid_5.xlsx
+++ b/data/source/Stainless_Steel_Carbon_Accounting_Grid_5.xlsx
@@ -576,10 +576,11 @@
     <row r="2" ht="65" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Reference database of emission/energy formulas per process. Cells in Columns D-N are PLAIN TEXT formula ENTRIES (not live Excel formulas): x=virgin ratio, y=scrap ratio(=1-x); a-g = grid electricity source shares (Coal/Oil/Gas/Hydro/Wind/Solar/Nuclear, sum to 1); p=train share, q=road share(=1-p), used ONLY in the two Transport-related rows (RMHS&gt;Unloading/Inbound and Outbound&gt;Transport) — all other rows show N/A for p/q. See 'Grid Energy Mix Factors' sheet for a-g source factors. Only Scope 2 (Col P) varies with the energy mix; Scope 1, Scope 3(upstream), trace-gas columns and SEC do not. Column Q = Scope 3 UPSTREAM (GHG Protocol Cat. 1-8); downstream Cat. 9 is in Outbound &gt; Transport; Cat. 10-15 are in the 'Downstream Scope 3 (Product)' sheet. GWP basis: IPCC AR5 (100-yr). GRID 5: coefficients recalibrated against published stainless-route benchmarks (see the 'Calibration Basis' sheet); rows, headers, variables and formula shapes are unchanged from Grid 4.</t>
-        </is>
-      </c>
-    </row>
+          <t>Reference database of emission/energy formulas per process. Cells in Columns D-N are PLAIN TEXT formula ENTRIES (not live Excel formulas): x=virgin ratio, y=scrap ratio(=1-x); a-g = grid electricity source shares (Coal/Oil/Gas/Hydro/Wind/Solar/Nuclear, sum to 1); p=train share, q=road share(=1-p), used ONLY in the two Transport-related rows (Inbound&gt;Unloading/Inbound and Outbound&gt;Transport) — all other rows show N/A for p/q. See 'Grid Energy Mix Factors' sheet for a-g source factors. Only Scope 2 (Col P) varies with the energy mix; Scope 1, Scope 3(upstream), trace-gas columns and SEC do not. Column Q = Scope 3 UPSTREAM (GHG Protocol Cat. 1-8); downstream Cat. 9 is in Outbound &gt; Transport; Cat. 10-15 are in the 'Downstream Scope 3 (Product)' sheet. GWP basis: IPCC AR5 (100-yr). GRID 5: coefficients recalibrated against published stainless-route benchmarks (see the 'Calibration Basis' sheet); rows, headers, variables and formula shapes are unchanged from Grid 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -739,7 +740,7 @@
     <row r="5" ht="190" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -874,7 +875,7 @@
     <row r="6" ht="140" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -999,7 +1000,7 @@
       </c>
       <c r="Z6" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.001, EF_S1_scrap=0.001 tCO2e/t | EF_S2_virgin=0.0009, EF_S2_scrap=0.0009 tCO2e/t | EF_S3_virgin=0.0005, EF_S3_scrap=0.0005 tCO2e/t
 CO2_v=0.0006, CO2_s=0.0006 t/t | CH4_v=0.000001, CH4_s=0.000001 t/t (x28) | N2O_v=0.00000005, N2O_s=0.00000005 t/t (x265)
 HFC_v=0.00002, HFC_s=0.00002 tCO2e/t | PFC_v=0.000005, PFC_s=0.000005 tCO2e/t | SF6_v=0.00000002, SF6_s=0.00000002 t/t (x23500) | NF3_v=0.00000001, NF3_s=0.00000001 t/t (x16100)
@@ -1013,7 +1014,7 @@
     <row r="7" ht="140" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1138,7 +1139,7 @@
       </c>
       <c r="Z7" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.001, EF_S1_scrap=0.0015 tCO2e/t | EF_S2_virgin=0.0009, EF_S2_scrap=0.0012 tCO2e/t | EF_S3_virgin=0.0005, EF_S3_scrap=0.0006 tCO2e/t
 CO2_v=0.0006, CO2_s=0.0009 t/t | CH4_v=0.000001, CH4_s=0.0000015 t/t (x28) | N2O_v=0.00000005, N2O_s=0.00000007 t/t (x265)
 HFC_v=0.00002, HFC_s=0.00002 tCO2e/t | PFC_v=0.000005, PFC_s=0.000005 tCO2e/t | SF6_v=0.00000002, SF6_s=0.00000002 t/t (x23500) | NF3_v=0.00000001, NF3_s=0.00000001 t/t (x16100)
@@ -1152,7 +1153,7 @@
     <row r="8" ht="140" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1277,12 +1278,12 @@
       </c>
       <c r="Z8" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.0007, EF_S1_scrap=0.01225 tCO2e/t | EF_S2_virgin=0.0006, EF_S2_scrap=0.0168 tCO2e/t | EF_S3_virgin=0.0005, EF_S3_scrap=0.002 tCO2e/t
 CO2_v=0.000525, CO2_s=0.0098 t/t | CH4_v=0.00000035, CH4_s=0.000014 t/t (x28) | N2O_v=0.0000000175, N2O_s=0.0000007 t/t (x265)
 HFC_v=0.000012, HFC_s=0.000018 tCO2e/t | PFC_v=0.000003, PFC_s=0.000006 tCO2e/t | SF6_v=0.000000012, SF6_s=0.00000003 t/t (x23500) | NF3_v=0.000000006, NF3_s=0.000000006 t/t (x16100)
 SEC_virgin=0.0122647 GJ/t, SEC_scrap=0.244086 GJ/t.
-Basis: Hydraulic shears/balers, oxy-fuel/propane cutting torches for oversize scrap, magnetic separation. Virgin ferroalloys rarely need this stage, hence near-zero virgin-side factors; scrap side is by far the most energy/emission-intensive process in RMHS due to shearing and thermal cutting. Generalized across all sub-variations of this process (none specified yet) — illustrative literature-typical values, NOT plant-measured.
+Basis: Hydraulic shears/balers, oxy-fuel/propane cutting torches for oversize scrap, magnetic separation. Virgin ferroalloys rarely need this stage, hence near-zero virgin-side factors; scrap side is by far the most energy/emission-intensive process in Inbound due to shearing and thermal cutting. Generalized across all sub-variations of this process (none specified yet) — illustrative literature-typical values, NOT plant-measured.
 Scope 2 CUSTOMIZED: underlying electricity intensity backed out at the CEA-baseline reference (0.77 kg CO2e/kWh) = 0.779221 kWh/t (virgin), 21.8182 kWh/t (scrap). Actual Scope 2 now scales with your real grid mix (a-g) — see 'Grid Energy Mix Factors' sheet for per-source factors.
 Grid 5 calibration: Scrap shredding and baling draws ~20-25 kWh per tonne of scrap; yard diesel for mobile handling ~3-5 L/t. Grid 4 → Grid 5 (virgin/scrap): kWh/t 1.2987/36.3636 → 0.779221/21.8182; Scope 1 0.002/0.035 → 0.0007/0.01225; SEC GJ/t 0.02/0.65 → 0.0122647/0.244086.</t>
         </is>
@@ -1291,7 +1292,7 @@
     <row r="9" ht="140" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1416,7 +1417,7 @@
       </c>
       <c r="Z9" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.0032, EF_S1_scrap=0.008 tCO2e/t | EF_S2_virgin=0.0035, EF_S2_scrap=0.00525 tCO2e/t | EF_S3_virgin=0.0005, EF_S3_scrap=0.0008 tCO2e/t
 CO2_v=0.002, CO2_s=0.0064 t/t | CH4_v=0.000002, CH4_s=0.000008 t/t (x28) | N2O_v=0.00000008, N2O_s=0.0000004 t/t (x265)
 HFC_v=0.000007, HFC_s=0.000007 tCO2e/t | PFC_v=0.00000175, PFC_s=0.0000028 tCO2e/t | SF6_v=0.0000000105, SF6_s=0.0000000105 t/t (x23500) | NF3_v=0.0000000035, NF3_s=0.0000000035 t/t (x16100)
@@ -1430,7 +1431,7 @@
     <row r="10" ht="140" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1555,7 +1556,7 @@
       </c>
       <c r="Z10" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.004, EF_S1_scrap=0.0032 tCO2e/t | EF_S2_virgin=0.0036, EF_S2_scrap=0.0015 tCO2e/t | EF_S3_virgin=0.0003, EF_S3_scrap=0.0003 tCO2e/t
 CO2_v=0.0036, CO2_s=0.0028 t/t | CH4_v=0.000006, CH4_s=0.000004 t/t (x28) | N2O_v=0.00000028, N2O_s=0.0000002 t/t (x265)
 HFC_v=0.000006, HFC_s=0.000006 tCO2e/t | PFC_v=0.0000015, PFC_s=0.0000015 tCO2e/t | SF6_v=0.000000015, SF6_s=0.000000009 t/t (x23500) | NF3_v=0.000000003, NF3_s=0.000000003 t/t (x16100)
@@ -1569,7 +1570,7 @@
     <row r="11" ht="140" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -1694,7 +1695,7 @@
       </c>
       <c r="Z11" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.001, EF_S1_scrap=0.002 tCO2e/t | EF_S2_virgin=0.0018, EF_S2_scrap=0.0036 tCO2e/t | EF_S3_virgin=0.0002, EF_S3_scrap=0.0002 tCO2e/t
 CO2_v=0.0008, CO2_s=0.0015 t/t | CH4_v=0.000001, CH4_s=0.000002 t/t (x28) | N2O_v=0.00000005, N2O_s=0.0000001 t/t (x265)
 HFC_v=0.000003, HFC_s=0.000003 tCO2e/t | PFC_v=0.0000009, PFC_s=0.0000009 tCO2e/t | SF6_v=0.000000015, SF6_s=0.000000024 t/t (x23500) | NF3_v=0.000000003, NF3_s=0.000000003 t/t (x16100)
@@ -1708,7 +1709,7 @@
     <row r="12" ht="140" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1833,7 +1834,7 @@
       </c>
       <c r="Z12" s="6" t="inlineStr">
         <is>
-          <t>Coefficients used in this row's formulas (Grid 5 calibration, RMHS materials-handling — replace with verified plant data before regulatory use):
+          <t>Coefficients used in this row's formulas (Grid 5 calibration, Inbound materials-handling — replace with verified plant data before regulatory use):
 EF_S1_virgin=0.0005, EF_S1_scrap=0.0008 tCO2e/t | EF_S2_virgin=0.00375, EF_S2_scrap=0.0045 tCO2e/t | EF_S3_virgin=0.0001, EF_S3_scrap=0.0001 tCO2e/t
 CO2_v=0.0004, CO2_s=0.0006 t/t | CH4_v=0.0000005, CH4_s=0.0000008 t/t (x28) | N2O_v=0.00000002, N2O_s=0.00000003 t/t (x265)
 HFC_v=0.0000025, HFC_s=0.0000025 tCO2e/t | PFC_v=0.0000005, PFC_s=0.0000005 tCO2e/t | SF6_v=0.00000001, SF6_s=0.00000001 t/t (x23500) | NF3_v=0.0000000025, NF3_s=0.0000000025 t/t (x16100)
@@ -1977,7 +1978,7 @@
 CO2_v=0.003, CO2_s=0.006 t/t | CH4_v=0.000002, CH4_s=0.000005 t/t (x28) | N2O_v=0.0000001, N2O_s=0.0000002 t/t (x265)
 HFC_v=0.000007, HFC_s=0.000007 tCO2e/t | PFC_v=0.00000105, PFC_s=0.00000105 tCO2e/t | SF6_v=0.0000000175, SF6_s=0.0000000175 t/t (x23500) | NF3_v=0.0000000035, NF3_s=0.0000000035 t/t (x16100)
 SEC_virgin=0.105649 GJ/t, SEC_scrap=0.219481 GJ/t.
-Basis: Melt-shop-side charging operation (as distinct from RMHS's yard proportioning) — charge-crane/basket handling and scrap preheating (waste-heat/electric) prior to furnace charging. Illustrative literature-typical values — NOT plant-measured.
+Basis: Melt-shop-side charging operation (as distinct from Inbound's yard proportioning) — charge-crane/basket handling and scrap preheating (waste-heat/electric) prior to furnace charging. Illustrative literature-typical values — NOT plant-measured.
 Scope 2 CUSTOMIZED: underlying electricity intensity backed out at the CEA-baseline reference (0.77 kg CO2e/kWh) = 4.54545 kWh/t (virgin), 11.3636 kWh/t (scrap). Actual Scope 2 now scales with your real grid mix (a-g) — see 'Grid Energy Mix Factors' sheet for per-source factors.
 Grid 5 calibration: Scrap charging cranes and magnets: ~4-10 kWh/t. Grid 4 → Grid 5 (virgin/scrap): kWh/t 12.987/32.4675 → 4.54545/11.3636; SEC GJ/t 0.15/0.25 → 0.105649/0.219481.</t>
         </is>
@@ -10083,6 +10084,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10219,6 +10221,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -10265,6 +10268,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10427,6 +10431,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="70" customHeight="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
@@ -10434,6 +10439,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="65" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
@@ -10492,6 +10498,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
         <is>
@@ -10815,6 +10822,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
@@ -10898,7 +10906,7 @@
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C25" s="16" t="inlineStr">
@@ -10933,7 +10941,7 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C26" s="16" t="inlineStr">
@@ -11000,7 +11008,7 @@
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C27" s="16" t="inlineStr">
@@ -11067,7 +11075,7 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C28" s="16" t="inlineStr">
@@ -11134,7 +11142,7 @@
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C29" s="16" t="inlineStr">
@@ -11201,7 +11209,7 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C30" s="16" t="inlineStr">
@@ -11268,7 +11276,7 @@
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C31" s="16" t="inlineStr">
@@ -11335,7 +11343,7 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>RMHS</t>
+          <t>Inbound</t>
         </is>
       </c>
       <c r="C32" s="16" t="inlineStr">
